--- a/database/event/8242/event_8242_evp_summary.xlsx
+++ b/database/event/8242/event_8242_evp_summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EVP_Summary_8242" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVP_Summary_8242" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per_Map_Scores" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -502,7 +502,7 @@
         <v>4.4355</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1389</v>
+        <v>3.5348</v>
       </c>
       <c r="E2" t="n">
         <v>9.792899999999999</v>
@@ -548,7 +548,7 @@
         <v>3.2735</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1896</v>
+        <v>2.4983</v>
       </c>
       <c r="E3" t="n">
         <v>7.2273</v>
@@ -594,7 +594,7 @@
         <v>3.1297</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0722</v>
+        <v>2.3701</v>
       </c>
       <c r="E4" t="n">
         <v>6.91</v>
@@ -640,7 +640,7 @@
         <v>2.6787</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7037</v>
+        <v>1.9678</v>
       </c>
       <c r="E5" t="n">
         <v>5.9141</v>
@@ -686,7 +686,7 @@
         <v>2.3761</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4565</v>
+        <v>1.6979</v>
       </c>
       <c r="E6" t="n">
         <v>5.2461</v>
@@ -732,7 +732,7 @@
         <v>2.232</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3389</v>
+        <v>1.5694</v>
       </c>
       <c r="E7" t="n">
         <v>4.928</v>
@@ -778,7 +778,7 @@
         <v>2.1964</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3097</v>
+        <v>1.5376</v>
       </c>
       <c r="E8" t="n">
         <v>4.8493</v>
@@ -824,7 +824,7 @@
         <v>2.1883</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3031</v>
+        <v>1.5305</v>
       </c>
       <c r="E9" t="n">
         <v>4.8315</v>
@@ -870,7 +870,7 @@
         <v>2.0721</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2082</v>
+        <v>1.4268</v>
       </c>
       <c r="E10" t="n">
         <v>4.5748</v>
@@ -916,7 +916,7 @@
         <v>2.0064</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1546</v>
+        <v>1.3682</v>
       </c>
       <c r="E11" t="n">
         <v>4.4299</v>
@@ -962,7 +962,7 @@
         <v>2.0049</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1533</v>
+        <v>1.3668</v>
       </c>
       <c r="E12" t="n">
         <v>4.4265</v>
@@ -1008,7 +1008,7 @@
         <v>1.9168</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0813</v>
+        <v>1.2883</v>
       </c>
       <c r="E13" t="n">
         <v>4.232</v>
@@ -1054,7 +1054,7 @@
         <v>1.7744</v>
       </c>
       <c r="D14" t="n">
-        <v>0.965</v>
+        <v>1.1613</v>
       </c>
       <c r="E14" t="n">
         <v>3.9177</v>
@@ -1100,7 +1100,7 @@
         <v>1.7098</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9122</v>
+        <v>1.1037</v>
       </c>
       <c r="E15" t="n">
         <v>3.775</v>
@@ -1146,7 +1146,7 @@
         <v>1.6122</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8325</v>
+        <v>1.0166</v>
       </c>
       <c r="E16" t="n">
         <v>3.5594</v>
@@ -1192,7 +1192,7 @@
         <v>1.5941</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8177</v>
+        <v>1.0005</v>
       </c>
       <c r="E17" t="n">
         <v>3.5196</v>
@@ -1238,7 +1238,7 @@
         <v>1.5515</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7829</v>
+        <v>0.9625</v>
       </c>
       <c r="E18" t="n">
         <v>3.4255</v>
@@ -1284,7 +1284,7 @@
         <v>1.5195</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7568</v>
+        <v>0.9339</v>
       </c>
       <c r="E19" t="n">
         <v>3.3549</v>
@@ -1330,7 +1330,7 @@
         <v>1.4351</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6878</v>
+        <v>0.8586</v>
       </c>
       <c r="E20" t="n">
         <v>3.1685</v>
@@ -1376,7 +1376,7 @@
         <v>1.4135</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6702</v>
+        <v>0.8394</v>
       </c>
       <c r="E21" t="n">
         <v>3.1209</v>
@@ -1422,7 +1422,7 @@
         <v>1.272</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5546</v>
+        <v>0.7131</v>
       </c>
       <c r="E22" t="n">
         <v>2.8083</v>
@@ -1468,7 +1468,7 @@
         <v>1.269</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5522</v>
+        <v>0.7105</v>
       </c>
       <c r="E23" t="n">
         <v>2.8018</v>
@@ -1514,7 +1514,7 @@
         <v>1.2095</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5036</v>
+        <v>0.6575</v>
       </c>
       <c r="E24" t="n">
         <v>2.6705</v>
@@ -1560,7 +1560,7 @@
         <v>1.208</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5023</v>
+        <v>0.6561</v>
       </c>
       <c r="E25" t="n">
         <v>2.6671</v>
@@ -1606,7 +1606,7 @@
         <v>1.1967</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4931</v>
+        <v>0.646</v>
       </c>
       <c r="E26" t="n">
         <v>2.6422</v>
@@ -1652,7 +1652,7 @@
         <v>1.1463</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4519</v>
+        <v>0.6011</v>
       </c>
       <c r="E27" t="n">
         <v>2.5309</v>
@@ -1698,7 +1698,7 @@
         <v>0.8354</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1979</v>
+        <v>0.3237</v>
       </c>
       <c r="E28" t="n">
         <v>1.8444</v>
@@ -1744,7 +1744,7 @@
         <v>0.8259</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1902</v>
+        <v>0.3153</v>
       </c>
       <c r="E29" t="n">
         <v>1.8235</v>
@@ -1790,7 +1790,7 @@
         <v>0.8233</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1881</v>
+        <v>0.313</v>
       </c>
       <c r="E30" t="n">
         <v>1.8178</v>
@@ -1836,7 +1836,7 @@
         <v>0.7457</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1247</v>
+        <v>0.2438</v>
       </c>
       <c r="E31" t="n">
         <v>1.6465</v>
@@ -1882,7 +1882,7 @@
         <v>0.742</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1217</v>
+        <v>0.2405</v>
       </c>
       <c r="E32" t="n">
         <v>1.6383</v>
@@ -1928,7 +1928,7 @@
         <v>0.5825</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.0982</v>
       </c>
       <c r="E33" t="n">
         <v>1.2861</v>
@@ -1974,7 +1974,7 @@
         <v>0.5383</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.0448</v>
+        <v>0.0588</v>
       </c>
       <c r="E34" t="n">
         <v>1.1885</v>
@@ -2020,7 +2020,7 @@
         <v>0.5256</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0551</v>
+        <v>0.0475</v>
       </c>
       <c r="E35" t="n">
         <v>1.1605</v>
@@ -2066,7 +2066,7 @@
         <v>0.5145999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.06419999999999999</v>
+        <v>0.0376</v>
       </c>
       <c r="E36" t="n">
         <v>1.1361</v>
@@ -2112,7 +2112,7 @@
         <v>0.5008</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.0253</v>
       </c>
       <c r="E37" t="n">
         <v>1.1057</v>
@@ -2158,7 +2158,7 @@
         <v>0.4227</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1392</v>
+        <v>-0.0443</v>
       </c>
       <c r="E38" t="n">
         <v>0.9333</v>
@@ -2204,7 +2204,7 @@
         <v>0.4205</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.141</v>
+        <v>-0.0463</v>
       </c>
       <c r="E39" t="n">
         <v>0.9285</v>
@@ -2250,7 +2250,7 @@
         <v>0.3926</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1638</v>
+        <v>-0.0712</v>
       </c>
       <c r="E40" t="n">
         <v>0.8667</v>
@@ -2296,7 +2296,7 @@
         <v>0.2954</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2432</v>
+        <v>-0.1579</v>
       </c>
       <c r="E41" t="n">
         <v>0.6521</v>
@@ -2342,7 +2342,7 @@
         <v>0.2781</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2574</v>
+        <v>-0.1734</v>
       </c>
       <c r="E42" t="n">
         <v>0.6139</v>
@@ -2388,7 +2388,7 @@
         <v>0.2468</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2829</v>
+        <v>-0.2012</v>
       </c>
       <c r="E43" t="n">
         <v>0.545</v>
@@ -2434,7 +2434,7 @@
         <v>0.2015</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3199</v>
+        <v>-0.2416</v>
       </c>
       <c r="E44" t="n">
         <v>0.4449</v>
@@ -2480,7 +2480,7 @@
         <v>0.1817</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3361</v>
+        <v>-0.2593</v>
       </c>
       <c r="E45" t="n">
         <v>0.4012</v>
@@ -2526,7 +2526,7 @@
         <v>0.1441</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3668</v>
+        <v>-0.2928</v>
       </c>
       <c r="E46" t="n">
         <v>0.3182</v>
@@ -2572,7 +2572,7 @@
         <v>0.1409</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3694</v>
+        <v>-0.2957</v>
       </c>
       <c r="E47" t="n">
         <v>0.311</v>
@@ -2618,7 +2618,7 @@
         <v>0.1313</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3772</v>
+        <v>-0.3042</v>
       </c>
       <c r="E48" t="n">
         <v>0.29</v>
@@ -2664,7 +2664,7 @@
         <v>0.1083</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.396</v>
+        <v>-0.3247</v>
       </c>
       <c r="E49" t="n">
         <v>0.2392</v>
@@ -2710,7 +2710,7 @@
         <v>0.0823</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4173</v>
+        <v>-0.348</v>
       </c>
       <c r="E50" t="n">
         <v>0.1817</v>
@@ -2756,7 +2756,7 @@
         <v>0.0813</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4181</v>
+        <v>-0.3489</v>
       </c>
       <c r="E51" t="n">
         <v>0.1794</v>
@@ -2802,7 +2802,7 @@
         <v>0.08</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4191</v>
+        <v>-0.35</v>
       </c>
       <c r="E52" t="n">
         <v>0.1767</v>
@@ -2848,7 +2848,7 @@
         <v>0.0789</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4201</v>
+        <v>-0.351</v>
       </c>
       <c r="E53" t="n">
         <v>0.1741</v>
@@ -2894,7 +2894,7 @@
         <v>0.0295</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4604</v>
+        <v>-0.395</v>
       </c>
       <c r="E54" t="n">
         <v>0.06519999999999999</v>
@@ -2940,7 +2940,7 @@
         <v>-0.0043</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.488</v>
+        <v>-0.4252</v>
       </c>
       <c r="E55" t="n">
         <v>-0.0095</v>
@@ -2986,7 +2986,7 @@
         <v>-0.099</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5654</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="E56" t="n">
         <v>-0.2185</v>
@@ -3032,7 +3032,7 @@
         <v>-0.107</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5719</v>
+        <v>-0.5168</v>
       </c>
       <c r="E57" t="n">
         <v>-0.2363</v>
@@ -3078,7 +3078,7 @@
         <v>-0.1103</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5746</v>
+        <v>-0.5198</v>
       </c>
       <c r="E58" t="n">
         <v>-0.2436</v>
@@ -3124,7 +3124,7 @@
         <v>-0.1239</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5857</v>
+        <v>-0.5319</v>
       </c>
       <c r="E59" t="n">
         <v>-0.2736</v>
@@ -3170,7 +3170,7 @@
         <v>-0.152</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6087</v>
+        <v>-0.5569</v>
       </c>
       <c r="E60" t="n">
         <v>-0.3356</v>
@@ -3216,7 +3216,7 @@
         <v>-0.1572</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6129</v>
+        <v>-0.5615</v>
       </c>
       <c r="E61" t="n">
         <v>-0.347</v>
@@ -3262,7 +3262,7 @@
         <v>-0.1732</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.626</v>
+        <v>-0.5758</v>
       </c>
       <c r="E62" t="n">
         <v>-0.3824</v>
@@ -3308,7 +3308,7 @@
         <v>-0.2915</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7227</v>
+        <v>-0.6814</v>
       </c>
       <c r="E63" t="n">
         <v>-0.6435999999999999</v>
@@ -3354,7 +3354,7 @@
         <v>-0.3014</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7307</v>
+        <v>-0.6902</v>
       </c>
       <c r="E64" t="n">
         <v>-0.6654</v>
@@ -3400,7 +3400,7 @@
         <v>-0.3693</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7862</v>
+        <v>-0.7508</v>
       </c>
       <c r="E65" t="n">
         <v>-0.8154</v>
@@ -3446,7 +3446,7 @@
         <v>-0.4222</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8294</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="E66" t="n">
         <v>-0.9321</v>
@@ -3492,7 +3492,7 @@
         <v>-0.4645</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.864</v>
+        <v>-0.8356</v>
       </c>
       <c r="E67" t="n">
         <v>-1.0255</v>
@@ -3538,7 +3538,7 @@
         <v>-0.4783</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8752</v>
+        <v>-0.848</v>
       </c>
       <c r="E68" t="n">
         <v>-1.056</v>
@@ -3584,7 +3584,7 @@
         <v>-0.5171</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9069</v>
+        <v>-0.8825</v>
       </c>
       <c r="E69" t="n">
         <v>-1.1416</v>
@@ -3630,7 +3630,7 @@
         <v>-0.5386</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9245</v>
+        <v>-0.9016999999999999</v>
       </c>
       <c r="E70" t="n">
         <v>-1.1891</v>
@@ -3676,7 +3676,7 @@
         <v>-0.5692</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9495</v>
+        <v>-0.9291</v>
       </c>
       <c r="E71" t="n">
         <v>-1.2568</v>
@@ -3722,7 +3722,7 @@
         <v>-0.5839</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9615</v>
+        <v>-0.9422</v>
       </c>
       <c r="E72" t="n">
         <v>-1.2892</v>
@@ -3768,7 +3768,7 @@
         <v>-0.5988</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9737</v>
+        <v>-0.9555</v>
       </c>
       <c r="E73" t="n">
         <v>-1.3221</v>
@@ -3814,7 +3814,7 @@
         <v>-0.6177</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9891</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="E74" t="n">
         <v>-1.3637</v>
@@ -3860,7 +3860,7 @@
         <v>-0.7066</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0617</v>
+        <v>-1.0516</v>
       </c>
       <c r="E75" t="n">
         <v>-1.56</v>
@@ -3906,7 +3906,7 @@
         <v>-0.737</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0866</v>
+        <v>-1.0787</v>
       </c>
       <c r="E76" t="n">
         <v>-1.6272</v>
@@ -3952,7 +3952,7 @@
         <v>-0.7736</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1164</v>
+        <v>-1.1113</v>
       </c>
       <c r="E77" t="n">
         <v>-1.7079</v>
@@ -3998,7 +3998,7 @@
         <v>-0.799</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1372</v>
+        <v>-1.134</v>
       </c>
       <c r="E78" t="n">
         <v>-1.7641</v>
@@ -4044,7 +4044,7 @@
         <v>-0.8538</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.182</v>
+        <v>-1.1829</v>
       </c>
       <c r="E79" t="n">
         <v>-1.885</v>
@@ -4090,7 +4090,7 @@
         <v>-1.0983</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.3817</v>
+        <v>-1.401</v>
       </c>
       <c r="E80" t="n">
         <v>-2.4249</v>
@@ -4136,7 +4136,7 @@
         <v>-1.1678</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.4385</v>
+        <v>-1.4629</v>
       </c>
       <c r="E81" t="n">
         <v>-2.5783</v>

--- a/database/event/8242/event_8242_evp_summary.xlsx
+++ b/database/event/8242/event_8242_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.792899999999999</v>
+        <v>9.7813</v>
       </c>
       <c r="C2" t="n">
-        <v>4.4355</v>
+        <v>4.4302</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5348</v>
+        <v>3.453</v>
       </c>
       <c r="E2" t="n">
-        <v>9.792899999999999</v>
+        <v>9.7813</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1066</v>
+        <v>3.095</v>
       </c>
       <c r="G2" t="n">
         <v>6.6863</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1066</v>
+        <v>3.095</v>
       </c>
       <c r="I2" t="n">
         <v>3.1211</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.2273</v>
+        <v>7.1993</v>
       </c>
       <c r="C3" t="n">
-        <v>3.2735</v>
+        <v>3.2608</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4983</v>
+        <v>2.4243</v>
       </c>
       <c r="E3" t="n">
-        <v>7.2273</v>
+        <v>7.1993</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7595</v>
+        <v>3.7315</v>
       </c>
       <c r="G3" t="n">
         <v>3.4679</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7595</v>
+        <v>3.7315</v>
       </c>
       <c r="I3" t="n">
         <v>3.7945</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.91</v>
+        <v>6.8826</v>
       </c>
       <c r="C4" t="n">
-        <v>3.1297</v>
+        <v>3.1173</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3701</v>
+        <v>2.2981</v>
       </c>
       <c r="E4" t="n">
-        <v>6.91</v>
+        <v>6.8826</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6872</v>
+        <v>3.6598</v>
       </c>
       <c r="G4" t="n">
         <v>3.2228</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6872</v>
+        <v>3.6598</v>
       </c>
       <c r="I4" t="n">
         <v>3.7216</v>
@@ -640,7 +640,7 @@
         <v>2.6787</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9678</v>
+        <v>1.9123</v>
       </c>
       <c r="E5" t="n">
         <v>5.9141</v>
@@ -686,7 +686,7 @@
         <v>2.3761</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6979</v>
+        <v>1.6461</v>
       </c>
       <c r="E6" t="n">
         <v>5.2461</v>
@@ -732,7 +732,7 @@
         <v>2.232</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5694</v>
+        <v>1.5194</v>
       </c>
       <c r="E7" t="n">
         <v>4.928</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.8493</v>
+        <v>4.8443</v>
       </c>
       <c r="C8" t="n">
-        <v>2.1964</v>
+        <v>2.1941</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5376</v>
+        <v>1.4861</v>
       </c>
       <c r="E8" t="n">
-        <v>4.8493</v>
+        <v>4.8443</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3471</v>
+        <v>1.3421</v>
       </c>
       <c r="G8" t="n">
         <v>3.5022</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3471</v>
+        <v>1.3421</v>
       </c>
       <c r="I8" t="n">
         <v>1.3534</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.8315</v>
+        <v>4.7981</v>
       </c>
       <c r="C9" t="n">
-        <v>2.1883</v>
+        <v>2.1732</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5305</v>
+        <v>1.4677</v>
       </c>
       <c r="E9" t="n">
-        <v>4.8315</v>
+        <v>4.7981</v>
       </c>
       <c r="F9" t="n">
-        <v>4.4614</v>
+        <v>4.428</v>
       </c>
       <c r="G9" t="n">
         <v>0.3701</v>
       </c>
       <c r="H9" t="n">
-        <v>4.6924</v>
+        <v>4.6401</v>
       </c>
       <c r="I9" t="n">
         <v>4.7582</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.5748</v>
+        <v>4.5435</v>
       </c>
       <c r="C10" t="n">
-        <v>2.0721</v>
+        <v>2.0579</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4268</v>
+        <v>1.3662</v>
       </c>
       <c r="E10" t="n">
-        <v>4.5748</v>
+        <v>4.5435</v>
       </c>
       <c r="F10" t="n">
-        <v>4.2787</v>
+        <v>4.2474</v>
       </c>
       <c r="G10" t="n">
         <v>0.2961</v>
       </c>
       <c r="H10" t="n">
-        <v>4.406</v>
+        <v>4.3568</v>
       </c>
       <c r="I10" t="n">
         <v>4.4678</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.4299</v>
+        <v>4.4189</v>
       </c>
       <c r="C11" t="n">
-        <v>2.0064</v>
+        <v>2.0014</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3682</v>
+        <v>1.3166</v>
       </c>
       <c r="E11" t="n">
-        <v>4.4299</v>
+        <v>4.4189</v>
       </c>
       <c r="F11" t="n">
-        <v>4.4299</v>
+        <v>4.4189</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>4.6431</v>
+        <v>4.6257</v>
       </c>
       <c r="I11" t="n">
         <v>4.6647</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.4265</v>
+        <v>4.417</v>
       </c>
       <c r="C12" t="n">
-        <v>2.0049</v>
+        <v>2.0006</v>
       </c>
       <c r="D12" t="n">
-        <v>1.3668</v>
+        <v>1.3158</v>
       </c>
       <c r="E12" t="n">
-        <v>4.4265</v>
+        <v>4.417</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5448</v>
+        <v>2.5353</v>
       </c>
       <c r="G12" t="n">
         <v>1.8817</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5448</v>
+        <v>2.5353</v>
       </c>
       <c r="I12" t="n">
         <v>2.5566</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.232</v>
+        <v>4.1901</v>
       </c>
       <c r="C13" t="n">
-        <v>1.9168</v>
+        <v>1.8978</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2883</v>
+        <v>1.2254</v>
       </c>
       <c r="E13" t="n">
-        <v>4.232</v>
+        <v>4.1901</v>
       </c>
       <c r="F13" t="n">
-        <v>5.2248</v>
+        <v>5.1829</v>
       </c>
       <c r="G13" t="n">
         <v>-0.9928</v>
       </c>
       <c r="H13" t="n">
-        <v>5.8895</v>
+        <v>5.8238</v>
       </c>
       <c r="I13" t="n">
         <v>5.9721</v>
@@ -1054,7 +1054,7 @@
         <v>1.7744</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1613</v>
+        <v>1.1169</v>
       </c>
       <c r="E14" t="n">
         <v>3.9177</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.775</v>
+        <v>3.7529</v>
       </c>
       <c r="C15" t="n">
-        <v>1.7098</v>
+        <v>1.6998</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1037</v>
+        <v>1.0512</v>
       </c>
       <c r="E15" t="n">
-        <v>3.775</v>
+        <v>3.7529</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9696</v>
+        <v>2.9475</v>
       </c>
       <c r="G15" t="n">
         <v>0.8054</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9696</v>
+        <v>2.9475</v>
       </c>
       <c r="I15" t="n">
         <v>2.9973</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.5594</v>
+        <v>3.5461</v>
       </c>
       <c r="C16" t="n">
-        <v>1.6122</v>
+        <v>1.6061</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0166</v>
+        <v>0.9689</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5594</v>
+        <v>3.5461</v>
       </c>
       <c r="F16" t="n">
-        <v>3.5594</v>
+        <v>3.5461</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.5594</v>
+        <v>3.5461</v>
       </c>
       <c r="I16" t="n">
         <v>3.576</v>
@@ -1192,7 +1192,7 @@
         <v>1.5941</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0005</v>
+        <v>0.9583</v>
       </c>
       <c r="E17" t="n">
         <v>3.5196</v>
@@ -1238,7 +1238,7 @@
         <v>1.5515</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9625</v>
+        <v>0.9208</v>
       </c>
       <c r="E18" t="n">
         <v>3.4255</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.3549</v>
+        <v>3.3227</v>
       </c>
       <c r="C19" t="n">
-        <v>1.5195</v>
+        <v>1.5049</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9339</v>
+        <v>0.8799</v>
       </c>
       <c r="E19" t="n">
-        <v>3.3549</v>
+        <v>3.3227</v>
       </c>
       <c r="F19" t="n">
-        <v>4.3549</v>
+        <v>4.3227</v>
       </c>
       <c r="G19" t="n">
         <v>-1</v>
       </c>
       <c r="H19" t="n">
-        <v>4.5254</v>
+        <v>4.475</v>
       </c>
       <c r="I19" t="n">
         <v>4.5889</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.1685</v>
+        <v>3.1567</v>
       </c>
       <c r="C20" t="n">
-        <v>1.4351</v>
+        <v>1.4298</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8586</v>
+        <v>0.8137</v>
       </c>
       <c r="E20" t="n">
-        <v>3.1685</v>
+        <v>3.1567</v>
       </c>
       <c r="F20" t="n">
-        <v>3.1685</v>
+        <v>3.1567</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3.1685</v>
+        <v>3.1567</v>
       </c>
       <c r="I20" t="n">
         <v>3.1832</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.1209</v>
+        <v>3.1073</v>
       </c>
       <c r="C21" t="n">
-        <v>1.4135</v>
+        <v>1.4074</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8394</v>
+        <v>0.794</v>
       </c>
       <c r="E21" t="n">
-        <v>3.1209</v>
+        <v>3.1073</v>
       </c>
       <c r="F21" t="n">
-        <v>1.821</v>
+        <v>1.8074</v>
       </c>
       <c r="G21" t="n">
         <v>1.2999</v>
       </c>
       <c r="H21" t="n">
-        <v>1.821</v>
+        <v>1.8074</v>
       </c>
       <c r="I21" t="n">
         <v>1.838</v>
@@ -1422,7 +1422,7 @@
         <v>1.272</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7131</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="E22" t="n">
         <v>2.8083</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.8018</v>
+        <v>2.7914</v>
       </c>
       <c r="C23" t="n">
-        <v>1.269</v>
+        <v>1.2643</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7105</v>
+        <v>0.6682</v>
       </c>
       <c r="E23" t="n">
-        <v>2.8018</v>
+        <v>2.7914</v>
       </c>
       <c r="F23" t="n">
-        <v>2.8018</v>
+        <v>2.7914</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.8018</v>
+        <v>2.7914</v>
       </c>
       <c r="I23" t="n">
         <v>2.8148</v>
@@ -1504,93 +1504,93 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>mizu</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.6705</v>
+        <v>2.6671</v>
       </c>
       <c r="C24" t="n">
-        <v>1.2095</v>
+        <v>1.208</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6575</v>
+        <v>0.6187</v>
       </c>
       <c r="E24" t="n">
-        <v>2.6705</v>
+        <v>2.6671</v>
       </c>
       <c r="F24" t="n">
-        <v>2.6705</v>
+        <v>2.6671</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.6705</v>
+        <v>2.6671</v>
       </c>
       <c r="I24" t="n">
-        <v>2.6829</v>
+        <v>2.6671</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>181</v>
+        <v>138</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.6829</v>
+        <v>2.6671</v>
       </c>
       <c r="N24" t="n">
-        <v>181</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mizu</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.6671</v>
+        <v>2.6605</v>
       </c>
       <c r="C25" t="n">
-        <v>1.208</v>
+        <v>1.205</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6561</v>
+        <v>0.616</v>
       </c>
       <c r="E25" t="n">
-        <v>2.6671</v>
+        <v>2.6605</v>
       </c>
       <c r="F25" t="n">
-        <v>2.6671</v>
+        <v>2.6605</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.6671</v>
+        <v>2.6605</v>
       </c>
       <c r="I25" t="n">
-        <v>2.6671</v>
+        <v>2.6829</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>138</v>
+        <v>181</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.6671</v>
+        <v>2.6829</v>
       </c>
       <c r="N25" t="n">
-        <v>138</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26">
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.6422</v>
+        <v>2.6487</v>
       </c>
       <c r="C26" t="n">
-        <v>1.1967</v>
+        <v>1.1997</v>
       </c>
       <c r="D26" t="n">
-        <v>0.646</v>
+        <v>0.6113</v>
       </c>
       <c r="E26" t="n">
-        <v>2.6422</v>
+        <v>2.6487</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.7448</v>
+        <v>-1.7383</v>
       </c>
       <c r="G26" t="n">
         <v>4.387</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.7448</v>
+        <v>-1.7383</v>
       </c>
       <c r="I26" t="n">
         <v>-1.7529</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.5309</v>
+        <v>2.5215</v>
       </c>
       <c r="C27" t="n">
-        <v>1.1463</v>
+        <v>1.1421</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6011</v>
+        <v>0.5607</v>
       </c>
       <c r="E27" t="n">
-        <v>2.5309</v>
+        <v>2.5215</v>
       </c>
       <c r="F27" t="n">
-        <v>2.5309</v>
+        <v>2.5215</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2.5309</v>
+        <v>2.5215</v>
       </c>
       <c r="I27" t="n">
         <v>2.5427</v>
@@ -1698,7 +1698,7 @@
         <v>0.8354</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3237</v>
+        <v>0.2909</v>
       </c>
       <c r="E28" t="n">
         <v>1.8444</v>
@@ -1744,7 +1744,7 @@
         <v>0.8259</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3153</v>
+        <v>0.2826</v>
       </c>
       <c r="E29" t="n">
         <v>1.8235</v>
@@ -1790,7 +1790,7 @@
         <v>0.8233</v>
       </c>
       <c r="D30" t="n">
-        <v>0.313</v>
+        <v>0.2803</v>
       </c>
       <c r="E30" t="n">
         <v>1.8178</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.6465</v>
+        <v>1.6404</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7457</v>
+        <v>0.743</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2438</v>
+        <v>0.2096</v>
       </c>
       <c r="E31" t="n">
-        <v>1.6465</v>
+        <v>1.6404</v>
       </c>
       <c r="F31" t="n">
-        <v>1.6465</v>
+        <v>1.6404</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.6465</v>
+        <v>1.6404</v>
       </c>
       <c r="I31" t="n">
         <v>1.6542</v>
@@ -1882,7 +1882,7 @@
         <v>0.742</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2405</v>
+        <v>0.2088</v>
       </c>
       <c r="E32" t="n">
         <v>1.6383</v>
@@ -1928,7 +1928,7 @@
         <v>0.5825</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0982</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="E33" t="n">
         <v>1.2861</v>
@@ -1974,7 +1974,7 @@
         <v>0.5383</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0588</v>
+        <v>0.0296</v>
       </c>
       <c r="E34" t="n">
         <v>1.1885</v>
@@ -2020,7 +2020,7 @@
         <v>0.5256</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0475</v>
+        <v>0.0184</v>
       </c>
       <c r="E35" t="n">
         <v>1.1605</v>
@@ -2066,7 +2066,7 @@
         <v>0.5145999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0376</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="E36" t="n">
         <v>1.1361</v>
@@ -2112,7 +2112,7 @@
         <v>0.5008</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0253</v>
+        <v>-0.0034</v>
       </c>
       <c r="E37" t="n">
         <v>1.1057</v>
@@ -2158,7 +2158,7 @@
         <v>0.4227</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0443</v>
+        <v>-0.0721</v>
       </c>
       <c r="E38" t="n">
         <v>0.9333</v>
@@ -2204,7 +2204,7 @@
         <v>0.4205</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0463</v>
+        <v>-0.074</v>
       </c>
       <c r="E39" t="n">
         <v>0.9285</v>
@@ -2250,7 +2250,7 @@
         <v>0.3926</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0712</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="E40" t="n">
         <v>0.8667</v>
@@ -2296,7 +2296,7 @@
         <v>0.2954</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.1579</v>
+        <v>-0.1841</v>
       </c>
       <c r="E41" t="n">
         <v>0.6521</v>
@@ -2342,7 +2342,7 @@
         <v>0.2781</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1734</v>
+        <v>-0.1993</v>
       </c>
       <c r="E42" t="n">
         <v>0.6139</v>
@@ -2388,7 +2388,7 @@
         <v>0.2468</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2012</v>
+        <v>-0.2268</v>
       </c>
       <c r="E43" t="n">
         <v>0.545</v>
@@ -2434,7 +2434,7 @@
         <v>0.2015</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2416</v>
+        <v>-0.2667</v>
       </c>
       <c r="E44" t="n">
         <v>0.4449</v>
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4012</v>
+        <v>0.3913</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1817</v>
+        <v>0.1772</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2593</v>
+        <v>-0.288</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4012</v>
+        <v>0.3913</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8842</v>
+        <v>0.8743</v>
       </c>
       <c r="G45" t="n">
         <v>-0.483</v>
       </c>
       <c r="H45" t="n">
-        <v>0.8842</v>
+        <v>0.8743</v>
       </c>
       <c r="I45" t="n">
         <v>0.8966</v>
@@ -2526,7 +2526,7 @@
         <v>0.1441</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2928</v>
+        <v>-0.3171</v>
       </c>
       <c r="E46" t="n">
         <v>0.3182</v>
@@ -2572,7 +2572,7 @@
         <v>0.1409</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2957</v>
+        <v>-0.32</v>
       </c>
       <c r="E47" t="n">
         <v>0.311</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.29</v>
+        <v>0.2854</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1313</v>
+        <v>0.1293</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3042</v>
+        <v>-0.3302</v>
       </c>
       <c r="E48" t="n">
-        <v>0.29</v>
+        <v>0.2854</v>
       </c>
       <c r="F48" t="n">
-        <v>1.2285</v>
+        <v>1.2239</v>
       </c>
       <c r="G48" t="n">
         <v>-0.9385</v>
       </c>
       <c r="H48" t="n">
-        <v>1.2285</v>
+        <v>1.2239</v>
       </c>
       <c r="I48" t="n">
         <v>1.2342</v>
@@ -2664,7 +2664,7 @@
         <v>0.1083</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3247</v>
+        <v>-0.3486</v>
       </c>
       <c r="E49" t="n">
         <v>0.2392</v>
@@ -2710,7 +2710,7 @@
         <v>0.0823</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.348</v>
+        <v>-0.3715</v>
       </c>
       <c r="E50" t="n">
         <v>0.1817</v>
@@ -2750,25 +2750,25 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.1794</v>
+        <v>0.1787</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0813</v>
+        <v>0.0809</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3489</v>
+        <v>-0.3727</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1794</v>
+        <v>0.1787</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1794</v>
+        <v>0.1787</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1794</v>
+        <v>0.1787</v>
       </c>
       <c r="I51" t="n">
         <v>0.1802</v>
@@ -2802,7 +2802,7 @@
         <v>0.08</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.35</v>
+        <v>-0.3735</v>
       </c>
       <c r="E52" t="n">
         <v>0.1767</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.1741</v>
+        <v>0.1734</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0789</v>
+        <v>0.0785</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.351</v>
+        <v>-0.3748</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1741</v>
+        <v>0.1734</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1741</v>
+        <v>0.1734</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1741</v>
+        <v>0.1734</v>
       </c>
       <c r="I53" t="n">
         <v>0.1749</v>
@@ -2894,7 +2894,7 @@
         <v>0.0295</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.395</v>
+        <v>-0.4179</v>
       </c>
       <c r="E54" t="n">
         <v>0.06519999999999999</v>
@@ -2940,7 +2940,7 @@
         <v>-0.0043</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4252</v>
+        <v>-0.4477</v>
       </c>
       <c r="E55" t="n">
         <v>-0.0095</v>
@@ -2986,7 +2986,7 @@
         <v>-0.099</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.531</v>
       </c>
       <c r="E56" t="n">
         <v>-0.2185</v>
@@ -3032,7 +3032,7 @@
         <v>-0.107</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5168</v>
+        <v>-0.5381</v>
       </c>
       <c r="E57" t="n">
         <v>-0.2363</v>
@@ -3078,7 +3078,7 @@
         <v>-0.1103</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5198</v>
+        <v>-0.541</v>
       </c>
       <c r="E58" t="n">
         <v>-0.2436</v>
@@ -3124,7 +3124,7 @@
         <v>-0.1239</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5319</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="E59" t="n">
         <v>-0.2736</v>
@@ -3170,7 +3170,7 @@
         <v>-0.152</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5569</v>
+        <v>-0.5776</v>
       </c>
       <c r="E60" t="n">
         <v>-0.3356</v>
@@ -3216,7 +3216,7 @@
         <v>-0.1572</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.5615</v>
+        <v>-0.5822000000000001</v>
       </c>
       <c r="E61" t="n">
         <v>-0.347</v>
@@ -3262,7 +3262,7 @@
         <v>-0.1732</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.5758</v>
+        <v>-0.5963000000000001</v>
       </c>
       <c r="E62" t="n">
         <v>-0.3824</v>
@@ -3308,7 +3308,7 @@
         <v>-0.2915</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6814</v>
+        <v>-0.7003</v>
       </c>
       <c r="E63" t="n">
         <v>-0.6435999999999999</v>
@@ -3354,7 +3354,7 @@
         <v>-0.3014</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6902</v>
+        <v>-0.709</v>
       </c>
       <c r="E64" t="n">
         <v>-0.6654</v>
@@ -3400,7 +3400,7 @@
         <v>-0.3693</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7508</v>
+        <v>-0.7688</v>
       </c>
       <c r="E65" t="n">
         <v>-0.8154</v>
@@ -3446,7 +3446,7 @@
         <v>-0.4222</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.8153</v>
       </c>
       <c r="E66" t="n">
         <v>-0.9321</v>
@@ -3492,7 +3492,7 @@
         <v>-0.4645</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8356</v>
+        <v>-0.8525</v>
       </c>
       <c r="E67" t="n">
         <v>-1.0255</v>
@@ -3538,7 +3538,7 @@
         <v>-0.4783</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.848</v>
+        <v>-0.8646</v>
       </c>
       <c r="E68" t="n">
         <v>-1.056</v>
@@ -3584,7 +3584,7 @@
         <v>-0.5171</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8825</v>
+        <v>-0.8987000000000001</v>
       </c>
       <c r="E69" t="n">
         <v>-1.1416</v>
@@ -3630,7 +3630,7 @@
         <v>-0.5386</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9016999999999999</v>
+        <v>-0.9176</v>
       </c>
       <c r="E70" t="n">
         <v>-1.1891</v>
@@ -3676,7 +3676,7 @@
         <v>-0.5692</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9291</v>
+        <v>-0.9446</v>
       </c>
       <c r="E71" t="n">
         <v>-1.2568</v>
@@ -3722,7 +3722,7 @@
         <v>-0.5839</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9422</v>
+        <v>-0.9575</v>
       </c>
       <c r="E72" t="n">
         <v>-1.2892</v>
@@ -3768,7 +3768,7 @@
         <v>-0.5988</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9555</v>
+        <v>-0.9706</v>
       </c>
       <c r="E73" t="n">
         <v>-1.3221</v>
@@ -3814,7 +3814,7 @@
         <v>-0.6177</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-0.9872</v>
       </c>
       <c r="E74" t="n">
         <v>-1.3637</v>
@@ -3854,25 +3854,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.56</v>
+        <v>-1.5542</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.7066</v>
+        <v>-0.7039</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0516</v>
+        <v>-1.0631</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.56</v>
+        <v>-1.5542</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.56</v>
+        <v>-1.5542</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.56</v>
+        <v>-1.5542</v>
       </c>
       <c r="I75" t="n">
         <v>-1.5673</v>
@@ -3906,7 +3906,7 @@
         <v>-0.737</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0787</v>
+        <v>-1.0922</v>
       </c>
       <c r="E76" t="n">
         <v>-1.6272</v>
@@ -3952,7 +3952,7 @@
         <v>-0.7736</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1113</v>
+        <v>-1.1243</v>
       </c>
       <c r="E77" t="n">
         <v>-1.7079</v>
@@ -3998,7 +3998,7 @@
         <v>-0.799</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.134</v>
+        <v>-1.1467</v>
       </c>
       <c r="E78" t="n">
         <v>-1.7641</v>
@@ -4044,7 +4044,7 @@
         <v>-0.8538</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.1829</v>
+        <v>-1.1949</v>
       </c>
       <c r="E79" t="n">
         <v>-1.885</v>
@@ -4090,7 +4090,7 @@
         <v>-1.0983</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.401</v>
+        <v>-1.41</v>
       </c>
       <c r="E80" t="n">
         <v>-2.4249</v>
@@ -4136,7 +4136,7 @@
         <v>-1.1678</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.4629</v>
+        <v>-1.4711</v>
       </c>
       <c r="E81" t="n">
         <v>-2.5783</v>

--- a/database/event/8242/event_8242_evp_summary.xlsx
+++ b/database/event/8242/event_8242_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.585000000000001</v>
+        <v>10.038</v>
       </c>
       <c r="C2" t="n">
-        <v>4.3413</v>
+        <v>4.5465</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7391</v>
+        <v>3.8699</v>
       </c>
       <c r="E2" t="n">
-        <v>9.585000000000001</v>
+        <v>10.038</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3942</v>
+        <v>3.3943</v>
       </c>
       <c r="G2" t="n">
         <v>6.1908</v>
       </c>
       <c r="H2" t="n">
-        <v>4.704</v>
+        <v>4.7041</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8252</v>
+        <v>4.8253</v>
       </c>
       <c r="J2" t="n">
         <v>7.9373</v>
@@ -529,7 +529,7 @@
         <v>152</v>
       </c>
       <c r="M2" t="n">
-        <v>12.7625</v>
+        <v>12.7626</v>
       </c>
       <c r="N2" t="n">
         <v>331</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.1344</v>
+        <v>7.2754</v>
       </c>
       <c r="C3" t="n">
-        <v>3.2314</v>
+        <v>3.2952</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6235</v>
+        <v>2.6359</v>
       </c>
       <c r="E3" t="n">
-        <v>7.1344</v>
+        <v>7.2754</v>
       </c>
       <c r="F3" t="n">
-        <v>3.9793</v>
+        <v>3.9794</v>
       </c>
       <c r="G3" t="n">
         <v>3.1551</v>
       </c>
       <c r="H3" t="n">
-        <v>5.9844</v>
+        <v>5.9847</v>
       </c>
       <c r="I3" t="n">
-        <v>6.2968</v>
+        <v>6.2971</v>
       </c>
       <c r="J3" t="n">
         <v>3.1551</v>
@@ -575,7 +575,7 @@
         <v>146</v>
       </c>
       <c r="M3" t="n">
-        <v>9.4519</v>
+        <v>9.452200000000001</v>
       </c>
       <c r="N3" t="n">
         <v>321</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.8312</v>
+        <v>6.9639</v>
       </c>
       <c r="C4" t="n">
-        <v>3.094</v>
+        <v>3.1542</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4855</v>
+        <v>2.4968</v>
       </c>
       <c r="E4" t="n">
-        <v>6.8312</v>
+        <v>6.9639</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3448</v>
+        <v>3.3428</v>
       </c>
       <c r="G4" t="n">
         <v>3.4864</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5957</v>
+        <v>4.5914</v>
       </c>
       <c r="I4" t="n">
-        <v>4.8356</v>
+        <v>4.8311</v>
       </c>
       <c r="J4" t="n">
         <v>3.4864</v>
@@ -621,7 +621,7 @@
         <v>146</v>
       </c>
       <c r="M4" t="n">
-        <v>8.322000000000001</v>
+        <v>8.317500000000001</v>
       </c>
       <c r="N4" t="n">
         <v>321</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.6513</v>
+        <v>5.9142</v>
       </c>
       <c r="C5" t="n">
-        <v>2.5596</v>
+        <v>2.6787</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9484</v>
+        <v>2.0279</v>
       </c>
       <c r="E5" t="n">
-        <v>5.6513</v>
+        <v>5.9142</v>
       </c>
       <c r="F5" t="n">
         <v>4.5807</v>
@@ -652,10 +652,10 @@
         <v>1.0706</v>
       </c>
       <c r="H5" t="n">
-        <v>17.1811</v>
+        <v>17.1697</v>
       </c>
       <c r="I5" t="n">
-        <v>9.2776</v>
+        <v>9.2715</v>
       </c>
       <c r="J5" t="n">
         <v>1.0706</v>
@@ -667,7 +667,7 @@
         <v>37</v>
       </c>
       <c r="M5" t="n">
-        <v>10.3482</v>
+        <v>10.3421</v>
       </c>
       <c r="N5" t="n">
         <v>229</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.3707</v>
+        <v>5.4579</v>
       </c>
       <c r="C6" t="n">
-        <v>2.4325</v>
+        <v>2.472</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8206</v>
+        <v>1.8241</v>
       </c>
       <c r="E6" t="n">
-        <v>5.3707</v>
+        <v>5.4579</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7937</v>
+        <v>1.7933</v>
       </c>
       <c r="G6" t="n">
-        <v>3.577</v>
+        <v>3.5955</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7937</v>
+        <v>1.7933</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8399</v>
+        <v>1.8395</v>
       </c>
       <c r="J6" t="n">
-        <v>3.577</v>
+        <v>3.5955</v>
       </c>
       <c r="K6" t="n">
         <v>179</v>
@@ -713,7 +713,7 @@
         <v>152</v>
       </c>
       <c r="M6" t="n">
-        <v>5.4169</v>
+        <v>5.435</v>
       </c>
       <c r="N6" t="n">
         <v>331</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.0005</v>
+        <v>4.9664</v>
       </c>
       <c r="C7" t="n">
-        <v>2.2649</v>
+        <v>2.2494</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6521</v>
+        <v>1.6046</v>
       </c>
       <c r="E7" t="n">
-        <v>5.0005</v>
+        <v>4.9664</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8682</v>
+        <v>3.9429</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1323</v>
+        <v>0.9739</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5527</v>
+        <v>8.1149</v>
       </c>
       <c r="I7" t="n">
-        <v>3.6443</v>
+        <v>4.382</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1323</v>
+        <v>0.9739</v>
       </c>
       <c r="K7" t="n">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="L7" t="n">
-        <v>152</v>
+        <v>46</v>
       </c>
       <c r="M7" t="n">
-        <v>5.7766</v>
+        <v>5.3559</v>
       </c>
       <c r="N7" t="n">
-        <v>331</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.9163</v>
+        <v>4.9177</v>
       </c>
       <c r="C8" t="n">
-        <v>2.2267</v>
+        <v>2.2274</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6138</v>
+        <v>1.5828</v>
       </c>
       <c r="E8" t="n">
-        <v>4.9163</v>
+        <v>4.9177</v>
       </c>
       <c r="F8" t="n">
-        <v>3.943</v>
+        <v>2.8625</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9733000000000001</v>
+        <v>2.1322</v>
       </c>
       <c r="H8" t="n">
-        <v>8.1151</v>
+        <v>3.5402</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3821</v>
+        <v>3.6314</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9733000000000001</v>
+        <v>2.1322</v>
       </c>
       <c r="K8" t="n">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="L8" t="n">
-        <v>46</v>
+        <v>152</v>
       </c>
       <c r="M8" t="n">
-        <v>5.3554</v>
+        <v>5.7636</v>
       </c>
       <c r="N8" t="n">
-        <v>232</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.5239</v>
+        <v>4.7216</v>
       </c>
       <c r="C9" t="n">
-        <v>2.049</v>
+        <v>2.1385</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4352</v>
+        <v>1.4952</v>
       </c>
       <c r="E9" t="n">
-        <v>4.5239</v>
+        <v>4.7216</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4305</v>
+        <v>3.4306</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0934</v>
+        <v>1.0939</v>
       </c>
       <c r="H9" t="n">
-        <v>6.4243</v>
+        <v>6.4246</v>
       </c>
       <c r="I9" t="n">
-        <v>3.469</v>
+        <v>3.4692</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0934</v>
+        <v>1.0939</v>
       </c>
       <c r="K9" t="n">
         <v>186</v>
@@ -851,7 +851,7 @@
         <v>46</v>
       </c>
       <c r="M9" t="n">
-        <v>4.5624</v>
+        <v>4.5631</v>
       </c>
       <c r="N9" t="n">
         <v>232</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.9602</v>
+        <v>4.1235</v>
       </c>
       <c r="C10" t="n">
-        <v>1.7937</v>
+        <v>1.8677</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1786</v>
+        <v>1.2281</v>
       </c>
       <c r="E10" t="n">
-        <v>3.9602</v>
+        <v>4.1235</v>
       </c>
       <c r="F10" t="n">
-        <v>4.6931</v>
+        <v>4.693</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7329</v>
       </c>
       <c r="H10" t="n">
-        <v>7.5467</v>
+        <v>7.5466</v>
       </c>
       <c r="I10" t="n">
-        <v>8.145300000000001</v>
+        <v>8.145200000000001</v>
       </c>
       <c r="J10" t="n">
         <v>-0.7329</v>
@@ -897,7 +897,7 @@
         <v>36</v>
       </c>
       <c r="M10" t="n">
-        <v>7.412400000000001</v>
+        <v>7.412300000000001</v>
       </c>
       <c r="N10" t="n">
         <v>246</v>
@@ -906,81 +906,81 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.8763</v>
+        <v>4.0639</v>
       </c>
       <c r="C11" t="n">
-        <v>1.7557</v>
+        <v>1.8407</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1404</v>
+        <v>1.2014</v>
       </c>
       <c r="E11" t="n">
-        <v>3.8763</v>
+        <v>4.0639</v>
       </c>
       <c r="F11" t="n">
-        <v>3.5049</v>
+        <v>3.7375</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3714</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>4.9461</v>
+        <v>5.4553</v>
       </c>
       <c r="I11" t="n">
-        <v>5.3384</v>
+        <v>5.5959</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3714</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="L11" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>5.7098</v>
+        <v>5.5959</v>
       </c>
       <c r="N11" t="n">
-        <v>246</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.855</v>
+        <v>3.9504</v>
       </c>
       <c r="C12" t="n">
-        <v>1.746</v>
+        <v>1.7893</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1307</v>
+        <v>1.1507</v>
       </c>
       <c r="E12" t="n">
-        <v>3.855</v>
+        <v>3.9504</v>
       </c>
       <c r="F12" t="n">
-        <v>3.6072</v>
+        <v>3.5143</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2478</v>
+        <v>0.3714</v>
       </c>
       <c r="H12" t="n">
-        <v>5.1701</v>
+        <v>4.9668</v>
       </c>
       <c r="I12" t="n">
-        <v>5.5802</v>
+        <v>5.3608</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2478</v>
+        <v>0.3714</v>
       </c>
       <c r="K12" t="n">
         <v>210</v>
@@ -989,7 +989,7 @@
         <v>36</v>
       </c>
       <c r="M12" t="n">
-        <v>5.827999999999999</v>
+        <v>5.732200000000001</v>
       </c>
       <c r="N12" t="n">
         <v>246</v>
@@ -998,81 +998,81 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.7758</v>
+        <v>3.912</v>
       </c>
       <c r="C13" t="n">
-        <v>1.7102</v>
+        <v>1.7719</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0946</v>
+        <v>1.1336</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7758</v>
+        <v>3.912</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2239</v>
+        <v>3.6072</v>
       </c>
       <c r="G13" t="n">
-        <v>1.5519</v>
+        <v>0.2478</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2239</v>
+        <v>5.17</v>
       </c>
       <c r="I13" t="n">
-        <v>2.34</v>
+        <v>5.5801</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5519</v>
+        <v>0.2478</v>
       </c>
       <c r="K13" t="n">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="L13" t="n">
-        <v>146</v>
+        <v>36</v>
       </c>
       <c r="M13" t="n">
-        <v>3.8919</v>
+        <v>5.8279</v>
       </c>
       <c r="N13" t="n">
-        <v>321</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.7678</v>
+        <v>3.8514</v>
       </c>
       <c r="C14" t="n">
-        <v>1.7065</v>
+        <v>1.7444</v>
       </c>
       <c r="D14" t="n">
-        <v>1.091</v>
+        <v>1.1065</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7678</v>
+        <v>3.8514</v>
       </c>
       <c r="F14" t="n">
-        <v>2.8398</v>
+        <v>2.2221</v>
       </c>
       <c r="G14" t="n">
-        <v>0.928</v>
+        <v>1.5519</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4905</v>
+        <v>2.2221</v>
       </c>
       <c r="I14" t="n">
-        <v>3.6727</v>
+        <v>2.3381</v>
       </c>
       <c r="J14" t="n">
-        <v>0.928</v>
+        <v>1.5519</v>
       </c>
       <c r="K14" t="n">
         <v>175</v>
@@ -1081,7 +1081,7 @@
         <v>146</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6007</v>
+        <v>3.89</v>
       </c>
       <c r="N14" t="n">
         <v>321</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.7376</v>
+        <v>3.7098</v>
       </c>
       <c r="C15" t="n">
-        <v>1.6929</v>
+        <v>1.6803</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0772</v>
+        <v>1.0433</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7376</v>
+        <v>3.7098</v>
       </c>
       <c r="F15" t="n">
-        <v>3.7376</v>
+        <v>3.7098</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.0493</v>
       </c>
       <c r="H15" t="n">
-        <v>5.4555</v>
+        <v>7.3457</v>
       </c>
       <c r="I15" t="n">
-        <v>5.5961</v>
+        <v>3.9666</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.0493</v>
       </c>
       <c r="K15" t="n">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M15" t="n">
-        <v>5.5961</v>
+        <v>3.9173</v>
       </c>
       <c r="N15" t="n">
-        <v>206</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.6664</v>
+        <v>3.6976</v>
       </c>
       <c r="C16" t="n">
-        <v>1.6606</v>
+        <v>1.6747</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0448</v>
+        <v>1.0378</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6664</v>
+        <v>3.6976</v>
       </c>
       <c r="F16" t="n">
-        <v>3.7157</v>
+        <v>2.835</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0493</v>
+        <v>0.928</v>
       </c>
       <c r="H16" t="n">
-        <v>7.3653</v>
+        <v>3.48</v>
       </c>
       <c r="I16" t="n">
-        <v>3.9772</v>
+        <v>3.6617</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0493</v>
+        <v>0.928</v>
       </c>
       <c r="K16" t="n">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="L16" t="n">
-        <v>37</v>
+        <v>146</v>
       </c>
       <c r="M16" t="n">
-        <v>3.9279</v>
+        <v>4.589700000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>229</v>
+        <v>321</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.3768</v>
+        <v>3.367</v>
       </c>
       <c r="C17" t="n">
-        <v>1.5295</v>
+        <v>1.525</v>
       </c>
       <c r="D17" t="n">
-        <v>0.913</v>
+        <v>0.8901</v>
       </c>
       <c r="E17" t="n">
-        <v>3.3768</v>
+        <v>3.367</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.997</v>
+        <v>-0.9618</v>
       </c>
       <c r="G17" t="n">
-        <v>4.3738</v>
+        <v>4.3645</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.997</v>
+        <v>-0.9618</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0227</v>
+        <v>-0.9866</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3738</v>
+        <v>4.3645</v>
       </c>
       <c r="K17" t="n">
         <v>179</v>
@@ -1219,7 +1219,7 @@
         <v>152</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3511</v>
+        <v>3.377899999999999</v>
       </c>
       <c r="N17" t="n">
         <v>331</v>
@@ -1228,783 +1228,783 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>YEKINDAR</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.3677</v>
+        <v>3.3663</v>
       </c>
       <c r="C18" t="n">
-        <v>1.5253</v>
+        <v>1.5247</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9088000000000001</v>
+        <v>0.8898</v>
       </c>
       <c r="E18" t="n">
-        <v>3.3677</v>
+        <v>3.3663</v>
       </c>
       <c r="F18" t="n">
-        <v>3.9014</v>
+        <v>2.9981</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5337</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>7.978</v>
+        <v>3.8369</v>
       </c>
       <c r="I18" t="n">
-        <v>4.308</v>
+        <v>3.9358</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5337</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="L18" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7743</v>
+        <v>3.9358</v>
       </c>
       <c r="N18" t="n">
-        <v>232</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>YEKINDAR</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.0225</v>
+        <v>3.3294</v>
       </c>
       <c r="C19" t="n">
-        <v>1.369</v>
+        <v>1.508</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7517</v>
+        <v>0.8733</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0225</v>
+        <v>3.3294</v>
       </c>
       <c r="F19" t="n">
-        <v>3.5246</v>
+        <v>3.903</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5021</v>
+        <v>-0.5453</v>
       </c>
       <c r="H19" t="n">
-        <v>6.7349</v>
+        <v>7.9832</v>
       </c>
       <c r="I19" t="n">
-        <v>3.6368</v>
+        <v>4.3108</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5021</v>
+        <v>-0.5453</v>
       </c>
       <c r="K19" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="L19" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1347</v>
+        <v>3.7655</v>
       </c>
       <c r="N19" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.0007</v>
+        <v>3.1008</v>
       </c>
       <c r="C20" t="n">
-        <v>1.3591</v>
+        <v>1.4044</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7418</v>
+        <v>0.7712</v>
       </c>
       <c r="E20" t="n">
-        <v>3.0007</v>
+        <v>3.1008</v>
       </c>
       <c r="F20" t="n">
-        <v>3.0007</v>
+        <v>2.8605</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3.8426</v>
+        <v>3.5358</v>
       </c>
       <c r="I20" t="n">
-        <v>3.9416</v>
+        <v>3.6269</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>206</v>
+        <v>181</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.9416</v>
+        <v>3.6269</v>
       </c>
       <c r="N20" t="n">
-        <v>206</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.9885</v>
+        <v>3.0142</v>
       </c>
       <c r="C21" t="n">
-        <v>1.3536</v>
+        <v>1.3652</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7362</v>
+        <v>0.7326</v>
       </c>
       <c r="E21" t="n">
-        <v>2.9885</v>
+        <v>3.0142</v>
       </c>
       <c r="F21" t="n">
-        <v>2.9885</v>
+        <v>3.0099</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.8159</v>
+        <v>3.8628</v>
       </c>
       <c r="I21" t="n">
-        <v>3.9142</v>
+        <v>3.9623</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9142</v>
+        <v>3.9623</v>
       </c>
       <c r="N21" t="n">
-        <v>181</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.8992</v>
+        <v>2.9987</v>
       </c>
       <c r="C22" t="n">
-        <v>1.3131</v>
+        <v>1.3582</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6956</v>
+        <v>0.7256</v>
       </c>
       <c r="E22" t="n">
-        <v>2.8992</v>
+        <v>2.9987</v>
       </c>
       <c r="F22" t="n">
-        <v>2.8992</v>
+        <v>3.5248</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.5021</v>
       </c>
       <c r="H22" t="n">
-        <v>3.6206</v>
+        <v>6.7355</v>
       </c>
       <c r="I22" t="n">
-        <v>3.7139</v>
+        <v>3.6371</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.5021</v>
       </c>
       <c r="K22" t="n">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M22" t="n">
-        <v>3.7139</v>
+        <v>3.135</v>
       </c>
       <c r="N22" t="n">
-        <v>206</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>mizu</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.8608</v>
+        <v>2.9946</v>
       </c>
       <c r="C23" t="n">
-        <v>1.2957</v>
+        <v>1.3563</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6781</v>
+        <v>0.7238</v>
       </c>
       <c r="E23" t="n">
-        <v>2.8608</v>
+        <v>2.9946</v>
       </c>
       <c r="F23" t="n">
-        <v>2.8608</v>
+        <v>2.6159</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3.5364</v>
+        <v>3.0005</v>
       </c>
       <c r="I23" t="n">
-        <v>3.6275</v>
+        <v>3.0005</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>181</v>
+        <v>138</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6275</v>
+        <v>3.0005</v>
       </c>
       <c r="N23" t="n">
-        <v>181</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.7123</v>
+        <v>2.9871</v>
       </c>
       <c r="C24" t="n">
-        <v>1.2285</v>
+        <v>1.3529</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6105</v>
+        <v>0.7205</v>
       </c>
       <c r="E24" t="n">
-        <v>2.7123</v>
+        <v>2.9871</v>
       </c>
       <c r="F24" t="n">
-        <v>3.6206</v>
+        <v>2.8895</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.9083</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>5.1994</v>
+        <v>3.5993</v>
       </c>
       <c r="I24" t="n">
-        <v>5.6118</v>
+        <v>3.6921</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9083</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="L24" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.7035</v>
+        <v>3.6921</v>
       </c>
       <c r="N24" t="n">
-        <v>246</v>
+        <v>206</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.6518</v>
+        <v>2.898</v>
       </c>
       <c r="C25" t="n">
-        <v>1.2011</v>
+        <v>1.3126</v>
       </c>
       <c r="D25" t="n">
-        <v>0.583</v>
+        <v>0.6807</v>
       </c>
       <c r="E25" t="n">
-        <v>2.6518</v>
+        <v>2.898</v>
       </c>
       <c r="F25" t="n">
-        <v>2.983</v>
+        <v>2.3876</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3312</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.804</v>
+        <v>2.5008</v>
       </c>
       <c r="I25" t="n">
-        <v>3.804</v>
+        <v>2.5008</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.3312</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="L25" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4728</v>
+        <v>2.5008</v>
       </c>
       <c r="N25" t="n">
-        <v>179</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.6277</v>
+        <v>2.8788</v>
       </c>
       <c r="C26" t="n">
-        <v>1.1902</v>
+        <v>1.3039</v>
       </c>
       <c r="D26" t="n">
-        <v>0.572</v>
+        <v>0.6721</v>
       </c>
       <c r="E26" t="n">
-        <v>2.6277</v>
+        <v>2.8788</v>
       </c>
       <c r="F26" t="n">
-        <v>2.6277</v>
+        <v>3.6206</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.9083</v>
       </c>
       <c r="H26" t="n">
-        <v>3.0263</v>
+        <v>5.1994</v>
       </c>
       <c r="I26" t="n">
-        <v>3.1043</v>
+        <v>5.6118</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.9083</v>
       </c>
       <c r="K26" t="n">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1043</v>
+        <v>4.7035</v>
       </c>
       <c r="N26" t="n">
-        <v>206</v>
+        <v>246</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>mizu</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.6109</v>
+        <v>2.7427</v>
       </c>
       <c r="C27" t="n">
-        <v>1.1826</v>
+        <v>1.2422</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5643</v>
+        <v>0.6113</v>
       </c>
       <c r="E27" t="n">
-        <v>2.6109</v>
+        <v>2.7427</v>
       </c>
       <c r="F27" t="n">
-        <v>2.6109</v>
+        <v>2.9827</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.3316</v>
       </c>
       <c r="H27" t="n">
-        <v>2.9895</v>
+        <v>3.8033</v>
       </c>
       <c r="I27" t="n">
-        <v>2.9895</v>
+        <v>3.8033</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.3316</v>
       </c>
       <c r="K27" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M27" t="n">
-        <v>2.9895</v>
+        <v>3.4717</v>
       </c>
       <c r="N27" t="n">
-        <v>138</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.4518</v>
+        <v>2.7326</v>
       </c>
       <c r="C28" t="n">
-        <v>1.1105</v>
+        <v>1.2377</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4919</v>
+        <v>0.6068</v>
       </c>
       <c r="E28" t="n">
-        <v>2.4518</v>
+        <v>2.7326</v>
       </c>
       <c r="F28" t="n">
-        <v>2.4518</v>
+        <v>2.6276</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2.6412</v>
+        <v>3.026</v>
       </c>
       <c r="I28" t="n">
-        <v>2.7093</v>
+        <v>3.104</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.7093</v>
+        <v>3.104</v>
       </c>
       <c r="N28" t="n">
-        <v>181</v>
+        <v>206</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>npl</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.3882</v>
+        <v>2.5466</v>
       </c>
       <c r="C29" t="n">
-        <v>1.0817</v>
+        <v>1.1534</v>
       </c>
       <c r="D29" t="n">
-        <v>0.463</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>2.3882</v>
+        <v>2.5466</v>
       </c>
       <c r="F29" t="n">
-        <v>2.3882</v>
+        <v>2.2153</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.502</v>
+        <v>2.2153</v>
       </c>
       <c r="I29" t="n">
-        <v>2.502</v>
+        <v>2.2153</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.502</v>
+        <v>2.2153</v>
       </c>
       <c r="N29" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>molodoy</t>
+          <t>s1zzi</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.2934</v>
+        <v>2.5323</v>
       </c>
       <c r="C30" t="n">
-        <v>1.0387</v>
+        <v>1.147</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4198</v>
+        <v>0.5173</v>
       </c>
       <c r="E30" t="n">
-        <v>2.2934</v>
+        <v>2.5323</v>
       </c>
       <c r="F30" t="n">
-        <v>3.2237</v>
+        <v>2.2775</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.9303</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>5.7418</v>
+        <v>2.2775</v>
       </c>
       <c r="I30" t="n">
-        <v>3.1006</v>
+        <v>2.2775</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.9303</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>186</v>
+        <v>125</v>
       </c>
       <c r="L30" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.1703</v>
+        <v>2.2775</v>
       </c>
       <c r="N30" t="n">
-        <v>232</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>s1zzi</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.2778</v>
+        <v>2.4808</v>
       </c>
       <c r="C31" t="n">
-        <v>1.0317</v>
+        <v>1.1236</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4127</v>
+        <v>0.4943</v>
       </c>
       <c r="E31" t="n">
-        <v>2.2778</v>
+        <v>2.4808</v>
       </c>
       <c r="F31" t="n">
-        <v>2.2778</v>
+        <v>2.4516</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.2778</v>
+        <v>2.6409</v>
       </c>
       <c r="I31" t="n">
-        <v>2.2778</v>
+        <v>2.709</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>125</v>
+        <v>181</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.2778</v>
+        <v>2.709</v>
       </c>
       <c r="N31" t="n">
-        <v>125</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>npl</t>
+          <t>molodoy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.2147</v>
+        <v>2.3019</v>
       </c>
       <c r="C32" t="n">
-        <v>1.0031</v>
+        <v>1.0426</v>
       </c>
       <c r="D32" t="n">
-        <v>0.384</v>
+        <v>0.4144</v>
       </c>
       <c r="E32" t="n">
-        <v>2.2147</v>
+        <v>2.3019</v>
       </c>
       <c r="F32" t="n">
-        <v>2.2147</v>
+        <v>3.2164</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.9301</v>
       </c>
       <c r="H32" t="n">
-        <v>2.2147</v>
+        <v>5.7181</v>
       </c>
       <c r="I32" t="n">
-        <v>2.2147</v>
+        <v>3.0877</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.9301</v>
       </c>
       <c r="K32" t="n">
-        <v>125</v>
+        <v>186</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M32" t="n">
-        <v>2.2147</v>
+        <v>2.1576</v>
       </c>
       <c r="N32" t="n">
-        <v>125</v>
+        <v>232</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.1345</v>
+        <v>2.2875</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9668</v>
+        <v>1.0361</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3475</v>
+        <v>0.408</v>
       </c>
       <c r="E33" t="n">
-        <v>2.1345</v>
+        <v>2.2875</v>
       </c>
       <c r="F33" t="n">
-        <v>1.1068</v>
+        <v>2.0173</v>
       </c>
       <c r="G33" t="n">
-        <v>1.0277</v>
+        <v>0.0852</v>
       </c>
       <c r="H33" t="n">
-        <v>1.1068</v>
+        <v>2.0173</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1646</v>
+        <v>2.0173</v>
       </c>
       <c r="J33" t="n">
-        <v>1.0277</v>
+        <v>0.0852</v>
       </c>
       <c r="K33" t="n">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="L33" t="n">
-        <v>146</v>
+        <v>39</v>
       </c>
       <c r="M33" t="n">
-        <v>2.1923</v>
+        <v>2.1025</v>
       </c>
       <c r="N33" t="n">
-        <v>321</v>
+        <v>179</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.1032</v>
+        <v>2.0002</v>
       </c>
       <c r="C34" t="n">
-        <v>0.9526</v>
+        <v>0.9059</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3332</v>
+        <v>0.2796</v>
       </c>
       <c r="E34" t="n">
-        <v>2.1032</v>
+        <v>2.0002</v>
       </c>
       <c r="F34" t="n">
-        <v>2.0178</v>
+        <v>1.1069</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0854</v>
+        <v>1.0277</v>
       </c>
       <c r="H34" t="n">
-        <v>2.0178</v>
+        <v>1.1069</v>
       </c>
       <c r="I34" t="n">
-        <v>2.0178</v>
+        <v>1.1647</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0854</v>
+        <v>1.0277</v>
       </c>
       <c r="K34" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="L34" t="n">
-        <v>39</v>
+        <v>146</v>
       </c>
       <c r="M34" t="n">
-        <v>2.1032</v>
+        <v>2.1924</v>
       </c>
       <c r="N34" t="n">
-        <v>179</v>
+        <v>321</v>
       </c>
     </row>
     <row r="35">
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.9445</v>
+        <v>1.8109</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8807</v>
+        <v>0.8202</v>
       </c>
       <c r="D35" t="n">
-        <v>0.261</v>
+        <v>0.1951</v>
       </c>
       <c r="E35" t="n">
-        <v>1.9445</v>
+        <v>1.8109</v>
       </c>
       <c r="F35" t="n">
-        <v>2.5715</v>
+        <v>2.5716</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.627</v>
+        <v>-0.6268</v>
       </c>
       <c r="H35" t="n">
-        <v>3.5901</v>
+        <v>3.5904</v>
       </c>
       <c r="I35" t="n">
-        <v>1.9386</v>
+        <v>1.9388</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.627</v>
+        <v>-0.6268</v>
       </c>
       <c r="K35" t="n">
         <v>186</v>
@@ -2047,7 +2047,7 @@
         <v>46</v>
       </c>
       <c r="M35" t="n">
-        <v>1.3116</v>
+        <v>1.312</v>
       </c>
       <c r="N35" t="n">
         <v>232</v>
@@ -2056,231 +2056,231 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kyousuke</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.8158</v>
+        <v>1.8069</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8224</v>
+        <v>0.8184</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2024</v>
+        <v>0.1933</v>
       </c>
       <c r="E36" t="n">
-        <v>1.8158</v>
+        <v>1.8069</v>
       </c>
       <c r="F36" t="n">
-        <v>2.3996</v>
+        <v>2.6675</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.5838</v>
+        <v>-0.8908</v>
       </c>
       <c r="H36" t="n">
-        <v>3.023</v>
+        <v>3.1134</v>
       </c>
       <c r="I36" t="n">
-        <v>1.6324</v>
+        <v>3.1134</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.5838</v>
+        <v>-0.8908</v>
       </c>
       <c r="K36" t="n">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L36" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M36" t="n">
-        <v>1.0486</v>
+        <v>2.2226</v>
       </c>
       <c r="N36" t="n">
-        <v>229</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>kyousuke</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.7776</v>
+        <v>1.7387</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8051</v>
+        <v>0.7875</v>
       </c>
       <c r="D37" t="n">
-        <v>0.185</v>
+        <v>0.1628</v>
       </c>
       <c r="E37" t="n">
-        <v>1.7776</v>
+        <v>1.7387</v>
       </c>
       <c r="F37" t="n">
-        <v>2.6681</v>
+        <v>2.4094</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.8905</v>
+        <v>-0.5838</v>
       </c>
       <c r="H37" t="n">
-        <v>3.1146</v>
+        <v>3.0553</v>
       </c>
       <c r="I37" t="n">
-        <v>3.1146</v>
+        <v>1.6498</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.8905</v>
+        <v>-0.5838</v>
       </c>
       <c r="K37" t="n">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="L37" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M37" t="n">
-        <v>2.2241</v>
+        <v>1.066</v>
       </c>
       <c r="N37" t="n">
-        <v>179</v>
+        <v>229</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>dumau</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.6318</v>
+        <v>1.7235</v>
       </c>
       <c r="C38" t="n">
-        <v>0.7391</v>
+        <v>0.7806</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1186</v>
+        <v>0.156</v>
       </c>
       <c r="E38" t="n">
-        <v>1.6318</v>
+        <v>1.7235</v>
       </c>
       <c r="F38" t="n">
-        <v>2.2554</v>
+        <v>1.3785</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.6236</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>2.5471</v>
+        <v>1.3785</v>
       </c>
       <c r="I38" t="n">
-        <v>1.3754</v>
+        <v>1.3785</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.6236</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>192</v>
+        <v>112</v>
       </c>
       <c r="L38" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.7517999999999999</v>
+        <v>1.3785</v>
       </c>
       <c r="N38" t="n">
-        <v>229</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>dav1g</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.4393</v>
+        <v>1.5299</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6519</v>
+        <v>0.6929</v>
       </c>
       <c r="D39" t="n">
-        <v>0.031</v>
+        <v>0.0696</v>
       </c>
       <c r="E39" t="n">
-        <v>1.4393</v>
+        <v>1.5299</v>
       </c>
       <c r="F39" t="n">
-        <v>1.4393</v>
+        <v>2.2447</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>-0.6236</v>
       </c>
       <c r="H39" t="n">
-        <v>1.4393</v>
+        <v>2.5118</v>
       </c>
       <c r="I39" t="n">
-        <v>1.4393</v>
+        <v>1.3564</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>-0.6236</v>
       </c>
       <c r="K39" t="n">
-        <v>120</v>
+        <v>192</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M39" t="n">
-        <v>1.4393</v>
+        <v>0.7328</v>
       </c>
       <c r="N39" t="n">
-        <v>120</v>
+        <v>229</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dumau</t>
+          <t>dav1g</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.3785</v>
+        <v>1.5097</v>
       </c>
       <c r="C40" t="n">
-        <v>0.6244</v>
+        <v>0.6838</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0033</v>
+        <v>0.0605</v>
       </c>
       <c r="E40" t="n">
-        <v>1.3785</v>
+        <v>1.5097</v>
       </c>
       <c r="F40" t="n">
-        <v>1.3785</v>
+        <v>1.4278</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.3785</v>
+        <v>1.4278</v>
       </c>
       <c r="I40" t="n">
-        <v>1.3785</v>
+        <v>1.4278</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.3785</v>
+        <v>1.4278</v>
       </c>
       <c r="N40" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41">
@@ -2290,16 +2290,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.2852</v>
+        <v>1.3075</v>
       </c>
       <c r="C41" t="n">
-        <v>0.5821</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0392</v>
+        <v>-0.0298</v>
       </c>
       <c r="E41" t="n">
-        <v>1.2852</v>
+        <v>1.3075</v>
       </c>
       <c r="F41" t="n">
         <v>1.2852</v>
@@ -2332,47 +2332,47 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>MartinezSa</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.2551</v>
+        <v>1.2422</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5685</v>
+        <v>0.5626</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.0529</v>
+        <v>-0.059</v>
       </c>
       <c r="E42" t="n">
-        <v>1.2551</v>
+        <v>1.2422</v>
       </c>
       <c r="F42" t="n">
-        <v>1.6289</v>
+        <v>1.1173</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.3738</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.6289</v>
+        <v>1.1173</v>
       </c>
       <c r="I42" t="n">
-        <v>1.7581</v>
+        <v>1.1173</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.3738</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="L42" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.3843</v>
+        <v>1.1173</v>
       </c>
       <c r="N42" t="n">
-        <v>246</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43">
@@ -2382,31 +2382,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.2095</v>
+        <v>1.1748</v>
       </c>
       <c r="C43" t="n">
-        <v>0.5478</v>
+        <v>0.5321</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.0736</v>
+        <v>-0.0891</v>
       </c>
       <c r="E43" t="n">
-        <v>1.2095</v>
+        <v>1.1748</v>
       </c>
       <c r="F43" t="n">
-        <v>1.1058</v>
+        <v>1.1151</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1037</v>
+        <v>0.128</v>
       </c>
       <c r="H43" t="n">
-        <v>1.1058</v>
+        <v>1.1151</v>
       </c>
       <c r="I43" t="n">
-        <v>1.1058</v>
+        <v>1.1151</v>
       </c>
       <c r="J43" t="n">
-        <v>0.1037</v>
+        <v>0.128</v>
       </c>
       <c r="K43" t="n">
         <v>140</v>
@@ -2415,7 +2415,7 @@
         <v>39</v>
       </c>
       <c r="M43" t="n">
-        <v>1.2095</v>
+        <v>1.2431</v>
       </c>
       <c r="N43" t="n">
         <v>179</v>
@@ -2424,47 +2424,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MartinezSa</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.1181</v>
+        <v>0.9901</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5064</v>
+        <v>0.4484</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1152</v>
+        <v>-0.1716</v>
       </c>
       <c r="E44" t="n">
-        <v>1.1181</v>
+        <v>0.9901</v>
       </c>
       <c r="F44" t="n">
-        <v>1.1181</v>
+        <v>1.6063</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>-0.3738</v>
       </c>
       <c r="H44" t="n">
-        <v>1.1181</v>
+        <v>1.6063</v>
       </c>
       <c r="I44" t="n">
-        <v>1.1181</v>
+        <v>1.7337</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>-0.3738</v>
       </c>
       <c r="K44" t="n">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M44" t="n">
-        <v>1.1181</v>
+        <v>1.3599</v>
       </c>
       <c r="N44" t="n">
-        <v>120</v>
+        <v>246</v>
       </c>
     </row>
     <row r="45">
@@ -2474,16 +2474,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8669</v>
+        <v>0.9332</v>
       </c>
       <c r="C45" t="n">
-        <v>0.3926</v>
+        <v>0.4227</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2296</v>
+        <v>-0.197</v>
       </c>
       <c r="E45" t="n">
-        <v>0.8669</v>
+        <v>0.9332</v>
       </c>
       <c r="F45" t="n">
         <v>0.8669</v>
@@ -2516,323 +2516,323 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>n0rb3r7</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8423</v>
+        <v>0.8256</v>
       </c>
       <c r="C46" t="n">
-        <v>0.3815</v>
+        <v>0.3739</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2408</v>
+        <v>-0.245</v>
       </c>
       <c r="E46" t="n">
-        <v>0.8423</v>
+        <v>0.8256</v>
       </c>
       <c r="F46" t="n">
-        <v>1.4978</v>
+        <v>0.7789</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.6555</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.4978</v>
+        <v>0.7789</v>
       </c>
       <c r="I46" t="n">
-        <v>1.5364</v>
+        <v>0.7789</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.6555</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c r="L46" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.8809</v>
+        <v>0.7789</v>
       </c>
       <c r="N46" t="n">
-        <v>331</v>
+        <v>138</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>soulfly</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7806</v>
+        <v>0.7147</v>
       </c>
       <c r="C47" t="n">
-        <v>0.3536</v>
+        <v>0.3237</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2689</v>
+        <v>-0.2946</v>
       </c>
       <c r="E47" t="n">
-        <v>0.7806</v>
+        <v>0.7147</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7806</v>
+        <v>1.4975</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>-0.6555</v>
       </c>
       <c r="H47" t="n">
-        <v>0.7806</v>
+        <v>1.4975</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8007</v>
+        <v>1.5361</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>-0.6555</v>
       </c>
       <c r="K47" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="M47" t="n">
-        <v>0.8007</v>
+        <v>0.8806</v>
       </c>
       <c r="N47" t="n">
-        <v>181</v>
+        <v>331</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>n0rb3r7</t>
+          <t>soulfly</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7792</v>
+        <v>0.5652</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3529</v>
+        <v>0.256</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2695</v>
+        <v>-0.3614</v>
       </c>
       <c r="E48" t="n">
-        <v>0.7792</v>
+        <v>0.5652</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7792</v>
+        <v>0.7804</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.7792</v>
+        <v>0.7804</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7792</v>
+        <v>0.8005</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>138</v>
+        <v>181</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.7792</v>
+        <v>0.8005</v>
       </c>
       <c r="N48" t="n">
-        <v>138</v>
+        <v>181</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>tAk</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5629</v>
+        <v>0.4249</v>
       </c>
       <c r="C49" t="n">
-        <v>0.255</v>
+        <v>0.1924</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.368</v>
+        <v>-0.424</v>
       </c>
       <c r="E49" t="n">
-        <v>0.5629</v>
+        <v>0.4249</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5629</v>
+        <v>0.4305</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.5629</v>
+        <v>0.4305</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5774</v>
+        <v>0.4305</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>206</v>
+        <v>87</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.5774</v>
+        <v>0.4305</v>
       </c>
       <c r="N49" t="n">
-        <v>206</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>mopoz</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5623</v>
+        <v>0.4229</v>
       </c>
       <c r="C50" t="n">
-        <v>0.2547</v>
+        <v>0.1915</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3682</v>
+        <v>-0.4249</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5623</v>
+        <v>0.4229</v>
       </c>
       <c r="F50" t="n">
-        <v>0.5623</v>
+        <v>0.4691</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5623</v>
+        <v>0.4691</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5623</v>
+        <v>0.4691</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.5623</v>
+        <v>0.4691</v>
       </c>
       <c r="N50" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>mopoz</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4696</v>
+        <v>0.3794</v>
       </c>
       <c r="C51" t="n">
-        <v>0.2127</v>
+        <v>0.1718</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4104</v>
+        <v>-0.4444</v>
       </c>
       <c r="E51" t="n">
-        <v>0.4696</v>
+        <v>0.3794</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4696</v>
+        <v>0.5618</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.4696</v>
+        <v>0.5618</v>
       </c>
       <c r="I51" t="n">
-        <v>0.4696</v>
+        <v>0.5618</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.4696</v>
+        <v>0.5618</v>
       </c>
       <c r="N51" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>tAk</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3923</v>
+        <v>0.3497</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1777</v>
+        <v>0.1584</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4456</v>
+        <v>-0.4576</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3923</v>
+        <v>0.3497</v>
       </c>
       <c r="F52" t="n">
-        <v>0.3923</v>
+        <v>0.5628</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.3923</v>
+        <v>0.5628</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3923</v>
+        <v>0.5773</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>87</v>
+        <v>206</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.3923</v>
+        <v>0.5773</v>
       </c>
       <c r="N52" t="n">
-        <v>87</v>
+        <v>206</v>
       </c>
     </row>
     <row r="53">
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.3332</v>
+        <v>0.2489</v>
       </c>
       <c r="C53" t="n">
-        <v>0.1509</v>
+        <v>0.1127</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4725</v>
+        <v>-0.5026</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3332</v>
+        <v>0.2489</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3332</v>
+        <v>0.3411</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.3332</v>
+        <v>0.3411</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3332</v>
+        <v>0.3411</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.3332</v>
+        <v>0.3411</v>
       </c>
       <c r="N53" t="n">
         <v>118</v>
@@ -2884,47 +2884,47 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.297</v>
+        <v>0.2351</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1345</v>
+        <v>0.1065</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.489</v>
+        <v>-0.5088</v>
       </c>
       <c r="E54" t="n">
-        <v>0.297</v>
+        <v>0.2351</v>
       </c>
       <c r="F54" t="n">
-        <v>0.297</v>
+        <v>-0.013</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.297</v>
+        <v>-0.013</v>
       </c>
       <c r="I54" t="n">
-        <v>0.297</v>
+        <v>-0.013</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.297</v>
+        <v>-0.013</v>
       </c>
       <c r="N54" t="n">
-        <v>87</v>
+        <v>155</v>
       </c>
     </row>
     <row r="55">
@@ -2934,16 +2934,16 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.1634</v>
+        <v>0.2154</v>
       </c>
       <c r="C55" t="n">
-        <v>0.074</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5498</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>0.1634</v>
+        <v>0.2154</v>
       </c>
       <c r="F55" t="n">
         <v>0.1634</v>
@@ -2976,139 +2976,139 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>frontales</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.1625</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0736</v>
+        <v>0.0433</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5502</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>0.1625</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1625</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1625</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1625</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.1625</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="N56" t="n">
-        <v>138</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.0654</v>
+        <v>0.0609</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0296</v>
+        <v>0.0276</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5944</v>
+        <v>-0.5866</v>
       </c>
       <c r="E57" t="n">
-        <v>0.0654</v>
+        <v>0.0609</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0654</v>
+        <v>0.2962</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.0654</v>
+        <v>0.2962</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0654</v>
+        <v>0.2962</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.0654</v>
+        <v>0.2962</v>
       </c>
       <c r="N57" t="n">
-        <v>120</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>alex666</t>
+          <t>frontales</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.0363</v>
+        <v>0.0325</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0164</v>
+        <v>0.0147</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6077</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>0.0363</v>
+        <v>0.0325</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0363</v>
+        <v>0.1619</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0363</v>
+        <v>0.1619</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0363</v>
+        <v>0.1619</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.0363</v>
+        <v>0.1619</v>
       </c>
       <c r="N58" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="59">
@@ -3118,16 +3118,16 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.0036</v>
+        <v>-0.124</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0016</v>
+        <v>-0.0562</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6226</v>
+        <v>-0.6692</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0036</v>
+        <v>-0.124</v>
       </c>
       <c r="F59" t="n">
         <v>0.0036</v>
@@ -3160,78 +3160,78 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>esenthial</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.013</v>
+        <v>-0.1656</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.0059</v>
+        <v>-0.075</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6301</v>
+        <v>-0.6878</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.013</v>
+        <v>-0.1656</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.013</v>
+        <v>-0.0762</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.013</v>
+        <v>-0.0762</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.013</v>
+        <v>-0.0762</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.013</v>
+        <v>-0.0762</v>
       </c>
       <c r="N60" t="n">
-        <v>155</v>
+        <v>125</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>esenthial</t>
+          <t>alex666</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.0761</v>
+        <v>-0.2119</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.0345</v>
+        <v>-0.096</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6588000000000001</v>
+        <v>-0.7085</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.0761</v>
+        <v>-0.2119</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.0761</v>
+        <v>0.0546</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.0761</v>
+        <v>0.0546</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.0761</v>
+        <v>0.0546</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.0761</v>
+        <v>0.0546</v>
       </c>
       <c r="N61" t="n">
         <v>125</v>
@@ -3252,32 +3252,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>latto</t>
+          <t>saadzin</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.2496</v>
+        <v>-0.3763</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.1131</v>
+        <v>-0.1704</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7378</v>
+        <v>-0.7819</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.2496</v>
+        <v>-0.3763</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.2496</v>
+        <v>-0.387</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.2496</v>
+        <v>-0.387</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.2496</v>
+        <v>-0.387</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.2496</v>
+        <v>-0.387</v>
       </c>
       <c r="N62" t="n">
         <v>112</v>
@@ -3298,446 +3298,446 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>sausol</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.2683</v>
+        <v>-0.4174</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1215</v>
+        <v>-0.1891</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7463</v>
+        <v>-0.8003</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.2683</v>
+        <v>-0.4174</v>
       </c>
       <c r="F63" t="n">
-        <v>0.6928</v>
+        <v>-0.2678</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.9611</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.6928</v>
+        <v>-0.2678</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6928</v>
+        <v>-0.2678</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.9611</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="L63" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.2683</v>
+        <v>-0.2678</v>
       </c>
       <c r="N63" t="n">
-        <v>179</v>
+        <v>120</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>sausol</t>
+          <t>kensizor</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.2795</v>
+        <v>-0.4478</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.1266</v>
+        <v>-0.2028</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7514</v>
+        <v>-0.8138</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.2795</v>
+        <v>-0.4478</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.2795</v>
+        <v>-0.391</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.2795</v>
+        <v>-0.391</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2795</v>
+        <v>-0.391</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.2795</v>
+        <v>-0.391</v>
       </c>
       <c r="N64" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>saadzin</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.387</v>
+        <v>-0.4897</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.1753</v>
+        <v>-0.2218</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8004</v>
+        <v>-0.8326</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.387</v>
+        <v>-0.4897</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.387</v>
+        <v>-0.6829</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.387</v>
+        <v>-0.6829</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.387</v>
+        <v>-0.6829</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.387</v>
+        <v>-0.6829</v>
       </c>
       <c r="N65" t="n">
-        <v>112</v>
+        <v>87</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kensizor</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.391</v>
+        <v>-0.5023</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.1771</v>
+        <v>-0.2275</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8022</v>
+        <v>-0.8381999999999999</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.391</v>
+        <v>-0.5023</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.391</v>
+        <v>0.7137</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>-0.9613</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.391</v>
+        <v>0.7137</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.391</v>
+        <v>0.7137</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>-0.9613</v>
       </c>
       <c r="K66" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.391</v>
+        <v>-0.2476</v>
       </c>
       <c r="N66" t="n">
-        <v>125</v>
+        <v>179</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kvem</t>
+          <t>latto</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.6395</v>
+        <v>-0.5209</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.2896</v>
+        <v>-0.2359</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9153</v>
+        <v>-0.8465</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.6395</v>
+        <v>-0.5209</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.6395</v>
+        <v>-0.2496</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.6395</v>
+        <v>-0.2496</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.6395</v>
+        <v>-0.2496</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.6395</v>
+        <v>-0.2496</v>
       </c>
       <c r="N67" t="n">
-        <v>74</v>
+        <v>112</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>dukefissura</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.6671</v>
+        <v>-0.739</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.3021</v>
+        <v>-0.3347</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9278999999999999</v>
+        <v>-0.9439</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.6671</v>
+        <v>-0.739</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.6671</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.6671</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.6671</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.6671</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="N68" t="n">
-        <v>138</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>Kvem</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.6677</v>
+        <v>-0.7562</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.3024</v>
+        <v>-0.3425</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9282</v>
+        <v>-0.9516</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.6677</v>
+        <v>-0.7562</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.6677</v>
+        <v>-0.6395</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.6677</v>
+        <v>-0.6395</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.6677</v>
+        <v>-0.6395</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.6677</v>
+        <v>-0.6395</v>
       </c>
       <c r="N69" t="n">
-        <v>118</v>
+        <v>74</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MAJ3R</t>
+          <t>dukefissura</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.6811</v>
+        <v>-0.8238</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.3085</v>
+        <v>-0.3731</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9343</v>
+        <v>-0.9818</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.6811</v>
+        <v>-0.8238</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.6811</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.6811</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6986</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>181</v>
+        <v>138</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.6986</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="N70" t="n">
-        <v>181</v>
+        <v>138</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>MAJ3R</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.6823</v>
+        <v>-0.8883</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.309</v>
+        <v>-0.4023</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9348</v>
+        <v>-1.0106</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.6823</v>
+        <v>-0.8883</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.6823</v>
+        <v>-0.6813</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.6823</v>
+        <v>-0.6813</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6823</v>
+        <v>-0.6989</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>87</v>
+        <v>181</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.6823</v>
+        <v>-0.6989</v>
       </c>
       <c r="N71" t="n">
-        <v>87</v>
+        <v>181</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.9171</v>
+        <v>-0.9949</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.4154</v>
+        <v>-0.4506</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0417</v>
+        <v>-1.0582</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.9171</v>
+        <v>-0.9949</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.9171</v>
+        <v>-1.0407</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.9171</v>
+        <v>-1.0407</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.9171</v>
+        <v>-1.0407</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.9171</v>
+        <v>-1.0407</v>
       </c>
       <c r="N72" t="n">
         <v>87</v>
@@ -3762,16 +3762,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.9235</v>
+        <v>-1.023</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.4183</v>
+        <v>-0.4633</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0446</v>
+        <v>-1.0708</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.9235</v>
+        <v>-1.023</v>
       </c>
       <c r="F73" t="n">
         <v>-0.9235</v>
@@ -3808,16 +3808,16 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.968</v>
+        <v>-1.0964</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.4384</v>
+        <v>-0.4966</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0649</v>
+        <v>-1.1036</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.968</v>
+        <v>-1.0964</v>
       </c>
       <c r="F74" t="n">
         <v>-0.968</v>
@@ -3850,32 +3850,32 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.0404</v>
+        <v>-1.3483</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.4712</v>
+        <v>-0.6107</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0978</v>
+        <v>-1.2161</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.0404</v>
+        <v>-1.3483</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.0404</v>
+        <v>-0.9175</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.0404</v>
+        <v>-0.9175</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.0404</v>
+        <v>-0.9175</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.0404</v>
+        <v>-0.9175</v>
       </c>
       <c r="N75" t="n">
         <v>87</v>
@@ -3900,16 +3900,16 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.3131</v>
+        <v>-1.4545</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.5947</v>
+        <v>-0.6588000000000001</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.222</v>
+        <v>-1.2635</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.3131</v>
+        <v>-1.4545</v>
       </c>
       <c r="F76" t="n">
         <v>-1.3131</v>
@@ -3942,93 +3942,93 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>reNTU</t>
+          <t>nicx</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.3915</v>
+        <v>-1.5763</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.6303</v>
+        <v>-0.714</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2576</v>
+        <v>-1.3179</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.3915</v>
+        <v>-1.5763</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.3915</v>
+        <v>-1.4706</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.3915</v>
+        <v>-1.4706</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.3915</v>
+        <v>-1.4706</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>155</v>
+        <v>74</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.3915</v>
+        <v>-1.4706</v>
       </c>
       <c r="N77" t="n">
-        <v>155</v>
+        <v>74</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>nicx</t>
+          <t>reNTU</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.4706</v>
+        <v>-1.5856</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.6661</v>
+        <v>-0.7181999999999999</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2937</v>
+        <v>-1.3221</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.4706</v>
+        <v>-1.5856</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.4706</v>
+        <v>-1.3915</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.4706</v>
+        <v>-1.3915</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.4706</v>
+        <v>-1.3915</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>74</v>
+        <v>155</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.4706</v>
+        <v>-1.3915</v>
       </c>
       <c r="N78" t="n">
-        <v>74</v>
+        <v>155</v>
       </c>
     </row>
     <row r="79">
@@ -4038,16 +4038,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.5267</v>
+        <v>-1.7442</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.6915</v>
+        <v>-0.79</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.3192</v>
+        <v>-1.3929</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.5267</v>
+        <v>-1.7442</v>
       </c>
       <c r="F79" t="n">
         <v>-1.5267</v>
@@ -4084,28 +4084,28 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.8526</v>
+        <v>-2.1707</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.8391</v>
+        <v>-0.9832</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.4675</v>
+        <v>-1.5834</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.8526</v>
+        <v>-2.1707</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.8526</v>
+        <v>-1.8439</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.8526</v>
+        <v>-1.8439</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.8526</v>
+        <v>-1.8439</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -4117,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>-1.8526</v>
+        <v>-1.8439</v>
       </c>
       <c r="N80" t="n">
         <v>138</v>
@@ -4130,28 +4130,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.1411</v>
+        <v>-2.6143</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.9698</v>
+        <v>-1.1841</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.5989</v>
+        <v>-1.7816</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.1411</v>
+        <v>-2.6143</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.1411</v>
+        <v>-2.1333</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.1411</v>
+        <v>-2.1333</v>
       </c>
       <c r="I81" t="n">
-        <v>-2.1411</v>
+        <v>-2.1333</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-2.1411</v>
+        <v>-2.1333</v>
       </c>
       <c r="N81" t="n">
         <v>118</v>
@@ -4466,13 +4466,13 @@
         <v>29</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1558</v>
+        <v>1.1739</v>
       </c>
       <c r="J7" t="n">
-        <v>33.5182</v>
+        <v>34.0431</v>
       </c>
     </row>
     <row r="8">
@@ -4509,10 +4509,10 @@
         <v>1.16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4623</v>
+        <v>0.4621</v>
       </c>
       <c r="J8" t="n">
-        <v>13.4067</v>
+        <v>13.4009</v>
       </c>
     </row>
     <row r="9">
@@ -4549,10 +4549,10 @@
         <v>1.07</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2373</v>
+        <v>0.237</v>
       </c>
       <c r="J9" t="n">
-        <v>6.8817</v>
+        <v>6.873</v>
       </c>
     </row>
     <row r="10">
@@ -4589,10 +4589,10 @@
         <v>1.06</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2085</v>
+        <v>0.2081</v>
       </c>
       <c r="J10" t="n">
-        <v>6.0465</v>
+        <v>6.0349</v>
       </c>
     </row>
     <row r="11">
@@ -4629,10 +4629,10 @@
         <v>0.95</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2279</v>
+        <v>-0.2283</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.6091</v>
+        <v>-6.6207</v>
       </c>
     </row>
     <row r="12">
@@ -5466,13 +5466,13 @@
         <v>24</v>
       </c>
       <c r="H32" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2701</v>
+        <v>1.2574</v>
       </c>
       <c r="J32" t="n">
-        <v>30.4824</v>
+        <v>30.1776</v>
       </c>
     </row>
     <row r="33">
@@ -5509,10 +5509,10 @@
         <v>1.6</v>
       </c>
       <c r="I33" t="n">
-        <v>1.2306</v>
+        <v>1.231</v>
       </c>
       <c r="J33" t="n">
-        <v>29.5344</v>
+        <v>29.544</v>
       </c>
     </row>
     <row r="34">
@@ -5549,10 +5549,10 @@
         <v>1.47</v>
       </c>
       <c r="I34" t="n">
-        <v>1.0546</v>
+        <v>1.055</v>
       </c>
       <c r="J34" t="n">
-        <v>25.3104</v>
+        <v>25.32</v>
       </c>
     </row>
     <row r="35">
@@ -5589,10 +5589,10 @@
         <v>0.8</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6316000000000001</v>
+        <v>-0.6313</v>
       </c>
       <c r="J35" t="n">
-        <v>-15.1584</v>
+        <v>-15.1512</v>
       </c>
     </row>
     <row r="36">
@@ -5629,10 +5629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8717</v>
+        <v>-0.8714</v>
       </c>
       <c r="J36" t="n">
-        <v>-20.9208</v>
+        <v>-20.9136</v>
       </c>
     </row>
     <row r="37">
@@ -6069,10 +6069,10 @@
         <v>1.78</v>
       </c>
       <c r="I47" t="n">
-        <v>1.1888</v>
+        <v>1.1894</v>
       </c>
       <c r="J47" t="n">
-        <v>28.5312</v>
+        <v>28.5456</v>
       </c>
     </row>
     <row r="48">
@@ -6109,10 +6109,10 @@
         <v>1.04</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1169</v>
+        <v>0.1172</v>
       </c>
       <c r="J48" t="n">
-        <v>2.8056</v>
+        <v>2.8128</v>
       </c>
     </row>
     <row r="49">
@@ -6146,13 +6146,13 @@
         <v>24</v>
       </c>
       <c r="H49" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.176</v>
+        <v>-0.1868</v>
       </c>
       <c r="J49" t="n">
-        <v>-4.224</v>
+        <v>-4.4832</v>
       </c>
     </row>
     <row r="50">
@@ -6189,10 +6189,10 @@
         <v>0.85</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2083</v>
+        <v>-0.2081</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.9992</v>
+        <v>-4.9944</v>
       </c>
     </row>
     <row r="51">
@@ -6229,10 +6229,10 @@
         <v>0.84</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2187</v>
+        <v>-0.2186</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.2488</v>
+        <v>-5.2464</v>
       </c>
     </row>
     <row r="52">
@@ -6669,10 +6669,10 @@
         <v>1.11</v>
       </c>
       <c r="I62" t="n">
-        <v>0.2996</v>
+        <v>0.3002</v>
       </c>
       <c r="J62" t="n">
-        <v>6.8908</v>
+        <v>6.9046</v>
       </c>
     </row>
     <row r="63">
@@ -6709,10 +6709,10 @@
         <v>1.03</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1216</v>
+        <v>0.1221</v>
       </c>
       <c r="J63" t="n">
-        <v>2.7968</v>
+        <v>2.8083</v>
       </c>
     </row>
     <row r="64">
@@ -6746,13 +6746,13 @@
         <v>23</v>
       </c>
       <c r="H64" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1154</v>
+        <v>-0.127</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.6542</v>
+        <v>-2.921</v>
       </c>
     </row>
     <row r="65">
@@ -6789,10 +6789,10 @@
         <v>0.73</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3086</v>
+        <v>-0.3084</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.0978</v>
+        <v>-7.0932</v>
       </c>
     </row>
     <row r="66">
@@ -6829,10 +6829,10 @@
         <v>0.63</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4001</v>
+        <v>-0.3999</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.202299999999999</v>
+        <v>-9.197699999999999</v>
       </c>
     </row>
     <row r="67">
@@ -8266,13 +8266,13 @@
         <v>19</v>
       </c>
       <c r="H102" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="I102" t="n">
-        <v>1.4608</v>
+        <v>1.4491</v>
       </c>
       <c r="J102" t="n">
-        <v>27.7552</v>
+        <v>27.5329</v>
       </c>
     </row>
     <row r="103">
@@ -8309,10 +8309,10 @@
         <v>1.44</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8567</v>
+        <v>0.857</v>
       </c>
       <c r="J103" t="n">
-        <v>16.2773</v>
+        <v>16.283</v>
       </c>
     </row>
     <row r="104">
@@ -8349,10 +8349,10 @@
         <v>1.14</v>
       </c>
       <c r="I104" t="n">
-        <v>0.3943</v>
+        <v>0.3947</v>
       </c>
       <c r="J104" t="n">
-        <v>7.4917</v>
+        <v>7.4993</v>
       </c>
     </row>
     <row r="105">
@@ -8389,10 +8389,10 @@
         <v>1.09</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2674</v>
+        <v>0.2677</v>
       </c>
       <c r="J105" t="n">
-        <v>5.0806</v>
+        <v>5.0863</v>
       </c>
     </row>
     <row r="106">
@@ -8429,10 +8429,10 @@
         <v>0.92</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3423</v>
+        <v>-0.342</v>
       </c>
       <c r="J106" t="n">
-        <v>-6.5037</v>
+        <v>-6.498</v>
       </c>
     </row>
     <row r="107">
@@ -8866,13 +8866,13 @@
         <v>18</v>
       </c>
       <c r="H117" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1988</v>
+        <v>0.2231</v>
       </c>
       <c r="J117" t="n">
-        <v>3.5784</v>
+        <v>4.0158</v>
       </c>
     </row>
     <row r="118">
@@ -8909,10 +8909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.0673</v>
+        <v>-0.0677</v>
       </c>
       <c r="J118" t="n">
-        <v>-1.2114</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="119">
@@ -8949,10 +8949,10 @@
         <v>0.77</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2571</v>
+        <v>-0.2573</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.6278</v>
+        <v>-4.6314</v>
       </c>
     </row>
     <row r="120">
@@ -8989,10 +8989,10 @@
         <v>0.48</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.5159</v>
       </c>
       <c r="J120" t="n">
-        <v>-9.280799999999999</v>
+        <v>-9.286199999999999</v>
       </c>
     </row>
     <row r="121">
@@ -9029,10 +9029,10 @@
         <v>0.44</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5503</v>
+        <v>-0.5505</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.9054</v>
+        <v>-9.909000000000001</v>
       </c>
     </row>
     <row r="122">
@@ -10069,10 +10069,10 @@
         <v>1.42</v>
       </c>
       <c r="I147" t="n">
-        <v>0.8265</v>
+        <v>0.8256</v>
       </c>
       <c r="J147" t="n">
-        <v>18.183</v>
+        <v>18.1632</v>
       </c>
     </row>
     <row r="148">
@@ -10109,10 +10109,10 @@
         <v>0.89</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1495</v>
+        <v>-0.1496</v>
       </c>
       <c r="J148" t="n">
-        <v>-3.289</v>
+        <v>-3.2912</v>
       </c>
     </row>
     <row r="149">
@@ -10146,13 +10146,13 @@
         <v>22</v>
       </c>
       <c r="H149" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2612</v>
+        <v>-0.2516</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.7464</v>
+        <v>-5.5352</v>
       </c>
     </row>
     <row r="150">
@@ -10189,10 +10189,10 @@
         <v>0.75</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.29</v>
+        <v>-0.2902</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.38</v>
+        <v>-6.3844</v>
       </c>
     </row>
     <row r="151">
@@ -10229,10 +10229,10 @@
         <v>0.59</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4358</v>
+        <v>-0.436</v>
       </c>
       <c r="J151" t="n">
-        <v>-9.5876</v>
+        <v>-9.592000000000001</v>
       </c>
     </row>
     <row r="152">
@@ -11669,10 +11669,10 @@
         <v>1.59</v>
       </c>
       <c r="I187" t="n">
-        <v>1.2262</v>
+        <v>1.2267</v>
       </c>
       <c r="J187" t="n">
-        <v>28.2026</v>
+        <v>28.2141</v>
       </c>
     </row>
     <row r="188">
@@ -11706,13 +11706,13 @@
         <v>23</v>
       </c>
       <c r="H188" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="I188" t="n">
-        <v>0.892</v>
+        <v>0.8729</v>
       </c>
       <c r="J188" t="n">
-        <v>20.516</v>
+        <v>20.0767</v>
       </c>
     </row>
     <row r="189">
@@ -11749,10 +11749,10 @@
         <v>1.27</v>
       </c>
       <c r="I189" t="n">
-        <v>0.6918</v>
+        <v>0.6921</v>
       </c>
       <c r="J189" t="n">
-        <v>15.9114</v>
+        <v>15.9183</v>
       </c>
     </row>
     <row r="190">
@@ -11789,10 +11789,10 @@
         <v>0.9</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3801</v>
+        <v>-0.3798</v>
       </c>
       <c r="J190" t="n">
-        <v>-8.7423</v>
+        <v>-8.7354</v>
       </c>
     </row>
     <row r="191">
@@ -11829,10 +11829,10 @@
         <v>0.87</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4577</v>
+        <v>-0.4574</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.5271</v>
+        <v>-10.5202</v>
       </c>
     </row>
     <row r="192">
@@ -12866,13 +12866,13 @@
         <v>20</v>
       </c>
       <c r="H217" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="I217" t="n">
-        <v>1.7741</v>
+        <v>1.7854</v>
       </c>
       <c r="J217" t="n">
-        <v>35.482</v>
+        <v>35.708</v>
       </c>
     </row>
     <row r="218">
@@ -12909,10 +12909,10 @@
         <v>1.49</v>
       </c>
       <c r="I218" t="n">
-        <v>1.0701</v>
+        <v>1.0698</v>
       </c>
       <c r="J218" t="n">
-        <v>21.402</v>
+        <v>21.396</v>
       </c>
     </row>
     <row r="219">
@@ -12949,10 +12949,10 @@
         <v>1.39</v>
       </c>
       <c r="I219" t="n">
-        <v>0.9089</v>
+        <v>0.9085</v>
       </c>
       <c r="J219" t="n">
-        <v>18.178</v>
+        <v>18.17</v>
       </c>
     </row>
     <row r="220">
@@ -12989,10 +12989,10 @@
         <v>1.03</v>
       </c>
       <c r="I220" t="n">
-        <v>0.0856</v>
+        <v>0.0853</v>
       </c>
       <c r="J220" t="n">
-        <v>1.712</v>
+        <v>1.706</v>
       </c>
     </row>
     <row r="221">
@@ -13029,10 +13029,10 @@
         <v>0.59</v>
       </c>
       <c r="I221" t="n">
-        <v>-1.084</v>
+        <v>-1.0842</v>
       </c>
       <c r="J221" t="n">
-        <v>-21.68</v>
+        <v>-21.684</v>
       </c>
     </row>
     <row r="222">
@@ -13469,10 +13469,10 @@
         <v>1.38</v>
       </c>
       <c r="I232" t="n">
-        <v>0.7598</v>
+        <v>0.7607</v>
       </c>
       <c r="J232" t="n">
-        <v>15.196</v>
+        <v>15.214</v>
       </c>
     </row>
     <row r="233">
@@ -13509,10 +13509,10 @@
         <v>0.96</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-0.0649</v>
       </c>
       <c r="J233" t="n">
-        <v>-1.302</v>
+        <v>-1.298</v>
       </c>
     </row>
     <row r="234">
@@ -13546,13 +13546,13 @@
         <v>20</v>
       </c>
       <c r="H234" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.2814</v>
+        <v>-0.2908</v>
       </c>
       <c r="J234" t="n">
-        <v>-5.628</v>
+        <v>-5.816</v>
       </c>
     </row>
     <row r="235">
@@ -13589,10 +13589,10 @@
         <v>0.74</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3004</v>
+        <v>-0.3002</v>
       </c>
       <c r="J235" t="n">
-        <v>-6.008</v>
+        <v>-6.004</v>
       </c>
     </row>
     <row r="236">
@@ -13629,10 +13629,10 @@
         <v>0.64</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3924</v>
+        <v>-0.3922</v>
       </c>
       <c r="J236" t="n">
-        <v>-7.848</v>
+        <v>-7.844</v>
       </c>
     </row>
     <row r="237">
@@ -13669,10 +13669,10 @@
         <v>1.9</v>
       </c>
       <c r="I237" t="n">
-        <v>1.589</v>
+        <v>1.5884</v>
       </c>
       <c r="J237" t="n">
-        <v>31.78</v>
+        <v>31.768</v>
       </c>
     </row>
     <row r="238">
@@ -13709,10 +13709,10 @@
         <v>1.34</v>
       </c>
       <c r="I238" t="n">
-        <v>0.8126</v>
+        <v>0.8124</v>
       </c>
       <c r="J238" t="n">
-        <v>16.252</v>
+        <v>16.248</v>
       </c>
     </row>
     <row r="239">
@@ -13746,13 +13746,13 @@
         <v>20</v>
       </c>
       <c r="H239" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="I239" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.5503</v>
       </c>
       <c r="J239" t="n">
-        <v>10.574</v>
+        <v>11.006</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>1.14</v>
       </c>
       <c r="I240" t="n">
-        <v>0.3903</v>
+        <v>0.39</v>
       </c>
       <c r="J240" t="n">
-        <v>7.806</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>1.05</v>
       </c>
       <c r="I241" t="n">
-        <v>0.1485</v>
+        <v>0.1482</v>
       </c>
       <c r="J241" t="n">
-        <v>2.97</v>
+        <v>2.964</v>
       </c>
     </row>
     <row r="242">
@@ -14669,10 +14669,10 @@
         <v>1.75</v>
       </c>
       <c r="I262" t="n">
-        <v>1.415</v>
+        <v>1.4155</v>
       </c>
       <c r="J262" t="n">
-        <v>31.13</v>
+        <v>31.141</v>
       </c>
     </row>
     <row r="263">
@@ -14709,10 +14709,10 @@
         <v>1.48</v>
       </c>
       <c r="I263" t="n">
-        <v>1.0615</v>
+        <v>1.0619</v>
       </c>
       <c r="J263" t="n">
-        <v>23.353</v>
+        <v>23.3618</v>
       </c>
     </row>
     <row r="264">
@@ -14749,10 +14749,10 @@
         <v>1.22</v>
       </c>
       <c r="I264" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.5793</v>
       </c>
       <c r="J264" t="n">
-        <v>12.7402</v>
+        <v>12.7446</v>
       </c>
     </row>
     <row r="265">
@@ -14789,10 +14789,10 @@
         <v>1.09</v>
       </c>
       <c r="I265" t="n">
-        <v>0.271</v>
+        <v>0.2713</v>
       </c>
       <c r="J265" t="n">
-        <v>5.962</v>
+        <v>5.9686</v>
       </c>
     </row>
     <row r="266">
@@ -14826,13 +14826,13 @@
         <v>22</v>
       </c>
       <c r="H266" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5201</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="J266" t="n">
-        <v>-11.4422</v>
+        <v>-11.9658</v>
       </c>
     </row>
     <row r="267">
@@ -14866,13 +14866,13 @@
         <v>22</v>
       </c>
       <c r="H267" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="I267" t="n">
-        <v>0.9961</v>
+        <v>1.0077</v>
       </c>
       <c r="J267" t="n">
-        <v>21.9142</v>
+        <v>22.1694</v>
       </c>
     </row>
     <row r="268">
@@ -14909,10 +14909,10 @@
         <v>1.3</v>
       </c>
       <c r="I268" t="n">
-        <v>0.61</v>
+        <v>0.6094000000000001</v>
       </c>
       <c r="J268" t="n">
-        <v>13.42</v>
+        <v>13.4068</v>
       </c>
     </row>
     <row r="269">
@@ -14949,10 +14949,10 @@
         <v>0.86</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1871</v>
+        <v>-0.1873</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.1162</v>
+        <v>-4.1206</v>
       </c>
     </row>
     <row r="270">
@@ -14989,10 +14989,10 @@
         <v>0.58</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4512</v>
+        <v>-0.4513</v>
       </c>
       <c r="J270" t="n">
-        <v>-9.926399999999999</v>
+        <v>-9.928599999999999</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.49</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5283</v>
+        <v>-0.5284</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.6226</v>
+        <v>-11.6248</v>
       </c>
     </row>
     <row r="272">
@@ -16069,10 +16069,10 @@
         <v>2.19</v>
       </c>
       <c r="I297" t="n">
-        <v>1.8725</v>
+        <v>1.873</v>
       </c>
       <c r="J297" t="n">
-        <v>28.0875</v>
+        <v>28.095</v>
       </c>
     </row>
     <row r="298">
@@ -16109,10 +16109,10 @@
         <v>1.71</v>
       </c>
       <c r="I298" t="n">
-        <v>1.3166</v>
+        <v>1.3168</v>
       </c>
       <c r="J298" t="n">
-        <v>19.749</v>
+        <v>19.752</v>
       </c>
     </row>
     <row r="299">
@@ -16146,13 +16146,13 @@
         <v>15</v>
       </c>
       <c r="H299" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="I299" t="n">
-        <v>0.9855</v>
+        <v>0.9694</v>
       </c>
       <c r="J299" t="n">
-        <v>14.7825</v>
+        <v>14.541</v>
       </c>
     </row>
     <row r="300">
@@ -16189,10 +16189,10 @@
         <v>1.43</v>
       </c>
       <c r="I300" t="n">
-        <v>0.9523</v>
+        <v>0.9526</v>
       </c>
       <c r="J300" t="n">
-        <v>14.2845</v>
+        <v>14.289</v>
       </c>
     </row>
     <row r="301">
@@ -16229,10 +16229,10 @@
         <v>1.01</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.028</v>
+        <v>-0.0277</v>
       </c>
       <c r="J301" t="n">
-        <v>-0.42</v>
+        <v>-0.4155</v>
       </c>
     </row>
     <row r="302">
@@ -16269,10 +16269,10 @@
         <v>1.64</v>
       </c>
       <c r="I302" t="n">
-        <v>1.2704</v>
+        <v>1.27</v>
       </c>
       <c r="J302" t="n">
-        <v>24.1376</v>
+        <v>24.13</v>
       </c>
     </row>
     <row r="303">
@@ -16309,10 +16309,10 @@
         <v>1.43</v>
       </c>
       <c r="I303" t="n">
-        <v>0.982</v>
+        <v>0.9816</v>
       </c>
       <c r="J303" t="n">
-        <v>18.658</v>
+        <v>18.6504</v>
       </c>
     </row>
     <row r="304">
@@ -16349,10 +16349,10 @@
         <v>1.3</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7391</v>
+        <v>0.739</v>
       </c>
       <c r="J304" t="n">
-        <v>14.0429</v>
+        <v>14.041</v>
       </c>
     </row>
     <row r="305">
@@ -16386,13 +16386,13 @@
         <v>19</v>
       </c>
       <c r="H305" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="I305" t="n">
-        <v>0.6189</v>
+        <v>0.6394</v>
       </c>
       <c r="J305" t="n">
-        <v>11.7591</v>
+        <v>12.1486</v>
       </c>
     </row>
     <row r="306">
@@ -16429,10 +16429,10 @@
         <v>0.87</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.4735</v>
+        <v>-0.4738</v>
       </c>
       <c r="J306" t="n">
-        <v>-8.996499999999999</v>
+        <v>-9.0022</v>
       </c>
     </row>
     <row r="307">
@@ -16709,10 +16709,10 @@
         <v>1.54</v>
       </c>
       <c r="I313" t="n">
-        <v>1.1076</v>
+        <v>1.1078</v>
       </c>
       <c r="J313" t="n">
-        <v>15.5064</v>
+        <v>15.5092</v>
       </c>
     </row>
     <row r="314">
@@ -16749,10 +16749,10 @@
         <v>1.52</v>
       </c>
       <c r="I314" t="n">
-        <v>1.0823</v>
+        <v>1.0825</v>
       </c>
       <c r="J314" t="n">
-        <v>15.1522</v>
+        <v>15.155</v>
       </c>
     </row>
     <row r="315">
@@ -16786,13 +16786,13 @@
         <v>14</v>
       </c>
       <c r="H315" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="I315" t="n">
-        <v>0.513</v>
+        <v>0.4913</v>
       </c>
       <c r="J315" t="n">
-        <v>7.182</v>
+        <v>6.8782</v>
       </c>
     </row>
     <row r="316">
@@ -16829,10 +16829,10 @@
         <v>1.01</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.0318</v>
+        <v>-0.0315</v>
       </c>
       <c r="J316" t="n">
-        <v>-0.4452</v>
+        <v>-0.441</v>
       </c>
     </row>
     <row r="317">
@@ -16869,10 +16869,10 @@
         <v>0.77</v>
       </c>
       <c r="I317" t="n">
-        <v>-0.2408</v>
+        <v>-0.2413</v>
       </c>
       <c r="J317" t="n">
-        <v>-3.3712</v>
+        <v>-3.3782</v>
       </c>
     </row>
     <row r="318">
@@ -16909,10 +16909,10 @@
         <v>0.7</v>
       </c>
       <c r="I318" t="n">
-        <v>-0.3099</v>
+        <v>-0.3102</v>
       </c>
       <c r="J318" t="n">
-        <v>-4.3386</v>
+        <v>-4.3428</v>
       </c>
     </row>
     <row r="319">
@@ -16946,13 +16946,13 @@
         <v>14</v>
       </c>
       <c r="H319" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.3638</v>
+        <v>-0.3555</v>
       </c>
       <c r="J319" t="n">
-        <v>-5.0932</v>
+        <v>-4.977</v>
       </c>
     </row>
     <row r="320">
@@ -16989,10 +16989,10 @@
         <v>0.6</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3976</v>
+        <v>-0.3979</v>
       </c>
       <c r="J320" t="n">
-        <v>-5.5664</v>
+        <v>-5.5706</v>
       </c>
     </row>
     <row r="321">
@@ -17029,10 +17029,10 @@
         <v>0.47</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5118</v>
+        <v>-0.512</v>
       </c>
       <c r="J321" t="n">
-        <v>-7.1652</v>
+        <v>-7.168</v>
       </c>
     </row>
     <row r="322">
@@ -18869,10 +18869,10 @@
         <v>0.87</v>
       </c>
       <c r="I367" t="n">
-        <v>-0.1253</v>
+        <v>-0.1259</v>
       </c>
       <c r="J367" t="n">
-        <v>-2.0048</v>
+        <v>-2.0144</v>
       </c>
     </row>
     <row r="368">
@@ -18909,10 +18909,10 @@
         <v>0.77</v>
       </c>
       <c r="I368" t="n">
-        <v>-0.2367</v>
+        <v>-0.2371</v>
       </c>
       <c r="J368" t="n">
-        <v>-3.7872</v>
+        <v>-3.7936</v>
       </c>
     </row>
     <row r="369">
@@ -18946,13 +18946,13 @@
         <v>16</v>
       </c>
       <c r="H369" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="I369" t="n">
-        <v>-0.3871</v>
+        <v>-0.3791</v>
       </c>
       <c r="J369" t="n">
-        <v>-6.1936</v>
+        <v>-6.0656</v>
       </c>
     </row>
     <row r="370">
@@ -18989,10 +18989,10 @@
         <v>0.54</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.4476</v>
+        <v>-0.4479</v>
       </c>
       <c r="J370" t="n">
-        <v>-7.1616</v>
+        <v>-7.1664</v>
       </c>
     </row>
     <row r="371">
@@ -19029,10 +19029,10 @@
         <v>0.3</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.6586</v>
+        <v>-0.6589</v>
       </c>
       <c r="J371" t="n">
-        <v>-10.5376</v>
+        <v>-10.5424</v>
       </c>
     </row>
     <row r="372">
@@ -19069,10 +19069,10 @@
         <v>0.89</v>
       </c>
       <c r="I372" t="n">
-        <v>-0.1361</v>
+        <v>-0.1367</v>
       </c>
       <c r="J372" t="n">
-        <v>-2.3137</v>
+        <v>-2.3239</v>
       </c>
     </row>
     <row r="373">
@@ -19106,13 +19106,13 @@
         <v>17</v>
       </c>
       <c r="H373" t="n">
-        <v>0.87</v>
+        <v>0.89</v>
       </c>
       <c r="I373" t="n">
-        <v>-0.1588</v>
+        <v>-0.1367</v>
       </c>
       <c r="J373" t="n">
-        <v>-2.6996</v>
+        <v>-2.3239</v>
       </c>
     </row>
     <row r="374">
@@ -19149,10 +19149,10 @@
         <v>0.78</v>
       </c>
       <c r="I374" t="n">
-        <v>-0.2509</v>
+        <v>-0.2512</v>
       </c>
       <c r="J374" t="n">
-        <v>-4.2653</v>
+        <v>-4.2704</v>
       </c>
     </row>
     <row r="375">
@@ -19189,10 +19189,10 @@
         <v>0.7</v>
       </c>
       <c r="I375" t="n">
-        <v>-0.324</v>
+        <v>-0.3245</v>
       </c>
       <c r="J375" t="n">
-        <v>-5.508</v>
+        <v>-5.5165</v>
       </c>
     </row>
     <row r="376">
@@ -19229,10 +19229,10 @@
         <v>0.6</v>
       </c>
       <c r="I376" t="n">
-        <v>-0.4142</v>
+        <v>-0.4147</v>
       </c>
       <c r="J376" t="n">
-        <v>-7.0414</v>
+        <v>-7.0499</v>
       </c>
     </row>
     <row r="377">
@@ -19269,16 +19269,16 @@
         <v>1.66</v>
       </c>
       <c r="I377" t="n">
-        <v>1.2784</v>
+        <v>1.2788</v>
       </c>
       <c r="J377" t="n">
-        <v>21.7328</v>
+        <v>21.7396</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>molodoy</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -19309,16 +19309,16 @@
         <v>1.56</v>
       </c>
       <c r="I378" t="n">
-        <v>1.1508</v>
+        <v>1.1511</v>
       </c>
       <c r="J378" t="n">
-        <v>19.5636</v>
+        <v>19.5687</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>molodoy</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -19346,13 +19346,13 @@
         <v>17</v>
       </c>
       <c r="H379" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="I379" t="n">
-        <v>1.1508</v>
+        <v>1.1382</v>
       </c>
       <c r="J379" t="n">
-        <v>19.5636</v>
+        <v>19.3494</v>
       </c>
     </row>
     <row r="380">
@@ -19389,10 +19389,10 @@
         <v>1.35</v>
       </c>
       <c r="I380" t="n">
-        <v>0.8257</v>
+        <v>0.8259</v>
       </c>
       <c r="J380" t="n">
-        <v>14.0369</v>
+        <v>14.0403</v>
       </c>
     </row>
     <row r="381">
@@ -19429,10 +19429,10 @@
         <v>0.82</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.6078</v>
+        <v>-0.6075</v>
       </c>
       <c r="J381" t="n">
-        <v>-10.3326</v>
+        <v>-10.3275</v>
       </c>
     </row>
     <row r="382">
@@ -19869,10 +19869,10 @@
         <v>1.62</v>
       </c>
       <c r="I392" t="n">
-        <v>1.2652</v>
+        <v>1.2647</v>
       </c>
       <c r="J392" t="n">
-        <v>27.8344</v>
+        <v>27.8234</v>
       </c>
     </row>
     <row r="393">
@@ -19909,10 +19909,10 @@
         <v>1.24</v>
       </c>
       <c r="I393" t="n">
-        <v>0.629</v>
+        <v>0.6287</v>
       </c>
       <c r="J393" t="n">
-        <v>13.838</v>
+        <v>13.8314</v>
       </c>
     </row>
     <row r="394">
@@ -19949,10 +19949,10 @@
         <v>1.18</v>
       </c>
       <c r="I394" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.5013</v>
       </c>
       <c r="J394" t="n">
-        <v>11.033</v>
+        <v>11.0286</v>
       </c>
     </row>
     <row r="395">
@@ -19986,13 +19986,13 @@
         <v>22</v>
       </c>
       <c r="H395" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="I395" t="n">
-        <v>0.228</v>
+        <v>0.2557</v>
       </c>
       <c r="J395" t="n">
-        <v>5.016</v>
+        <v>5.6254</v>
       </c>
     </row>
     <row r="396">
@@ -20029,10 +20029,10 @@
         <v>0.91</v>
       </c>
       <c r="I396" t="n">
-        <v>-0.3539</v>
+        <v>-0.3542</v>
       </c>
       <c r="J396" t="n">
-        <v>-7.7858</v>
+        <v>-7.7924</v>
       </c>
     </row>
     <row r="397">
@@ -21069,10 +21069,10 @@
         <v>1.52</v>
       </c>
       <c r="I422" t="n">
-        <v>1.0151</v>
+        <v>1.0129</v>
       </c>
       <c r="J422" t="n">
-        <v>18.2718</v>
+        <v>18.2322</v>
       </c>
     </row>
     <row r="423">
@@ -21106,13 +21106,13 @@
         <v>18</v>
       </c>
       <c r="H423" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="I423" t="n">
-        <v>0.5333</v>
+        <v>0.5491</v>
       </c>
       <c r="J423" t="n">
-        <v>9.599399999999999</v>
+        <v>9.883800000000001</v>
       </c>
     </row>
     <row r="424">
@@ -21149,10 +21149,10 @@
         <v>0.53</v>
       </c>
       <c r="I424" t="n">
-        <v>-0.4804</v>
+        <v>-0.4808</v>
       </c>
       <c r="J424" t="n">
-        <v>-8.6472</v>
+        <v>-8.654400000000001</v>
       </c>
     </row>
     <row r="425">
@@ -21186,13 +21186,13 @@
         <v>18</v>
       </c>
       <c r="H425" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="I425" t="n">
-        <v>-0.5322</v>
+        <v>-0.524</v>
       </c>
       <c r="J425" t="n">
-        <v>-9.579599999999999</v>
+        <v>-9.432</v>
       </c>
     </row>
     <row r="426">
@@ -21229,10 +21229,10 @@
         <v>0.3</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.6756</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="J426" t="n">
-        <v>-12.1608</v>
+        <v>-12.1662</v>
       </c>
     </row>
     <row r="427">
@@ -21866,13 +21866,13 @@
         <v>18</v>
       </c>
       <c r="H442" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="I442" t="n">
-        <v>0.2861</v>
+        <v>0.3057</v>
       </c>
       <c r="J442" t="n">
-        <v>5.1498</v>
+        <v>5.5026</v>
       </c>
     </row>
     <row r="443">
@@ -21909,10 +21909,10 @@
         <v>1.04</v>
       </c>
       <c r="I443" t="n">
-        <v>0.1529</v>
+        <v>0.1524</v>
       </c>
       <c r="J443" t="n">
-        <v>2.7522</v>
+        <v>2.7432</v>
       </c>
     </row>
     <row r="444">
@@ -21949,10 +21949,10 @@
         <v>0.85</v>
       </c>
       <c r="I444" t="n">
-        <v>-0.1895</v>
+        <v>-0.1896</v>
       </c>
       <c r="J444" t="n">
-        <v>-3.411</v>
+        <v>-3.4128</v>
       </c>
     </row>
     <row r="445">
@@ -21989,10 +21989,10 @@
         <v>0.68</v>
       </c>
       <c r="I445" t="n">
-        <v>-0.3527</v>
+        <v>-0.3529</v>
       </c>
       <c r="J445" t="n">
-        <v>-6.3486</v>
+        <v>-6.3522</v>
       </c>
     </row>
     <row r="446">
@@ -22029,10 +22029,10 @@
         <v>0.64</v>
       </c>
       <c r="I446" t="n">
-        <v>-0.3889</v>
+        <v>-0.3891</v>
       </c>
       <c r="J446" t="n">
-        <v>-7.0002</v>
+        <v>-7.0038</v>
       </c>
     </row>
     <row r="447">
@@ -22109,10 +22109,10 @@
         <v>1.42</v>
       </c>
       <c r="I448" t="n">
-        <v>0.9475</v>
+        <v>0.9476</v>
       </c>
       <c r="J448" t="n">
-        <v>17.055</v>
+        <v>17.0568</v>
       </c>
     </row>
     <row r="449">
@@ -22149,10 +22149,10 @@
         <v>1.34</v>
       </c>
       <c r="I449" t="n">
-        <v>0.7996</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="J449" t="n">
-        <v>14.3928</v>
+        <v>14.3982</v>
       </c>
     </row>
     <row r="450">
@@ -22186,13 +22186,13 @@
         <v>18</v>
       </c>
       <c r="H450" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="I450" t="n">
-        <v>0.4196</v>
+        <v>0.3963</v>
       </c>
       <c r="J450" t="n">
-        <v>7.5528</v>
+        <v>7.1334</v>
       </c>
     </row>
     <row r="451">
@@ -22229,10 +22229,10 @@
         <v>0.84</v>
       </c>
       <c r="I451" t="n">
-        <v>-0.5681</v>
+        <v>-0.5678</v>
       </c>
       <c r="J451" t="n">
-        <v>-10.2258</v>
+        <v>-10.2204</v>
       </c>
     </row>
     <row r="452">
@@ -23069,10 +23069,10 @@
         <v>1.31</v>
       </c>
       <c r="I472" t="n">
-        <v>0.8073</v>
+        <v>0.8066</v>
       </c>
       <c r="J472" t="n">
-        <v>19.3752</v>
+        <v>19.3584</v>
       </c>
     </row>
     <row r="473">
@@ -23109,10 +23109,10 @@
         <v>1.28</v>
       </c>
       <c r="I473" t="n">
-        <v>0.7441</v>
+        <v>0.7435</v>
       </c>
       <c r="J473" t="n">
-        <v>17.8584</v>
+        <v>17.844</v>
       </c>
     </row>
     <row r="474">
@@ -23146,13 +23146,13 @@
         <v>24</v>
       </c>
       <c r="H474" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I474" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.1267</v>
       </c>
       <c r="J474" t="n">
-        <v>2.1816</v>
+        <v>3.0408</v>
       </c>
     </row>
     <row r="475">
@@ -23189,10 +23189,10 @@
         <v>1.01</v>
       </c>
       <c r="I475" t="n">
-        <v>0.0498</v>
+        <v>0.0495</v>
       </c>
       <c r="J475" t="n">
-        <v>1.1952</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="476">
@@ -23229,10 +23229,10 @@
         <v>0.71</v>
       </c>
       <c r="I476" t="n">
-        <v>-0.8007</v>
+        <v>-0.8011</v>
       </c>
       <c r="J476" t="n">
-        <v>-19.2168</v>
+        <v>-19.2264</v>
       </c>
     </row>
     <row r="477">
@@ -24546,13 +24546,13 @@
         <v>23</v>
       </c>
       <c r="H509" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="I509" t="n">
-        <v>-0.1309</v>
+        <v>-0.1192</v>
       </c>
       <c r="J509" t="n">
-        <v>-3.0107</v>
+        <v>-2.7416</v>
       </c>
     </row>
     <row r="510">
@@ -24586,13 +24586,13 @@
         <v>23</v>
       </c>
       <c r="H510" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="I510" t="n">
-        <v>-0.1309</v>
+        <v>-0.1423</v>
       </c>
       <c r="J510" t="n">
-        <v>-3.0107</v>
+        <v>-3.2729</v>
       </c>
     </row>
     <row r="511">
@@ -25269,10 +25269,10 @@
         <v>1.73</v>
       </c>
       <c r="I527" t="n">
-        <v>1.1524</v>
+        <v>1.1518</v>
       </c>
       <c r="J527" t="n">
-        <v>33.4196</v>
+        <v>33.4022</v>
       </c>
     </row>
     <row r="528">
@@ -25309,10 +25309,10 @@
         <v>1.27</v>
       </c>
       <c r="I528" t="n">
-        <v>0.5404</v>
+        <v>0.5399</v>
       </c>
       <c r="J528" t="n">
-        <v>15.6716</v>
+        <v>15.6571</v>
       </c>
     </row>
     <row r="529">
@@ -25349,10 +25349,10 @@
         <v>0.9</v>
       </c>
       <c r="I529" t="n">
-        <v>-0.15</v>
+        <v>-0.1502</v>
       </c>
       <c r="J529" t="n">
-        <v>-4.35</v>
+        <v>-4.3558</v>
       </c>
     </row>
     <row r="530">
@@ -25386,13 +25386,13 @@
         <v>29</v>
       </c>
       <c r="H530" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I530" t="n">
-        <v>-0.369</v>
+        <v>-0.3601</v>
       </c>
       <c r="J530" t="n">
-        <v>-10.701</v>
+        <v>-10.4429</v>
       </c>
     </row>
     <row r="531">
@@ -25429,10 +25429,10 @@
         <v>0.6</v>
       </c>
       <c r="I531" t="n">
-        <v>-0.4401</v>
+        <v>-0.4402</v>
       </c>
       <c r="J531" t="n">
-        <v>-12.7629</v>
+        <v>-12.7658</v>
       </c>
     </row>
     <row r="532">
@@ -26869,10 +26869,10 @@
         <v>1.64</v>
       </c>
       <c r="I567" t="n">
-        <v>1.2953</v>
+        <v>1.2948</v>
       </c>
       <c r="J567" t="n">
-        <v>29.7919</v>
+        <v>29.7804</v>
       </c>
     </row>
     <row r="568">
@@ -26909,10 +26909,10 @@
         <v>1.35</v>
       </c>
       <c r="I568" t="n">
-        <v>0.855</v>
+        <v>0.8546</v>
       </c>
       <c r="J568" t="n">
-        <v>19.665</v>
+        <v>19.6558</v>
       </c>
     </row>
     <row r="569">
@@ -26946,13 +26946,13 @@
         <v>23</v>
       </c>
       <c r="H569" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="I569" t="n">
-        <v>0.5674</v>
+        <v>0.5885</v>
       </c>
       <c r="J569" t="n">
-        <v>13.0502</v>
+        <v>13.5355</v>
       </c>
     </row>
     <row r="570">
@@ -26989,10 +26989,10 @@
         <v>1.07</v>
       </c>
       <c r="I570" t="n">
-        <v>0.2303</v>
+        <v>0.23</v>
       </c>
       <c r="J570" t="n">
-        <v>5.2969</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="571">
@@ -27029,10 +27029,10 @@
         <v>0.68</v>
       </c>
       <c r="I571" t="n">
-        <v>-0.8854</v>
+        <v>-0.8857</v>
       </c>
       <c r="J571" t="n">
-        <v>-20.3642</v>
+        <v>-20.3711</v>
       </c>
     </row>
     <row r="572">
@@ -28669,10 +28669,10 @@
         <v>1.53</v>
       </c>
       <c r="I612" t="n">
-        <v>0.9307</v>
+        <v>0.93</v>
       </c>
       <c r="J612" t="n">
-        <v>21.4061</v>
+        <v>21.39</v>
       </c>
     </row>
     <row r="613">
@@ -28706,13 +28706,13 @@
         <v>23</v>
       </c>
       <c r="H613" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="I613" t="n">
-        <v>0.2478</v>
+        <v>0.2667</v>
       </c>
       <c r="J613" t="n">
-        <v>5.6994</v>
+        <v>6.1341</v>
       </c>
     </row>
     <row r="614">
@@ -28749,10 +28749,10 @@
         <v>1</v>
       </c>
       <c r="I614" t="n">
-        <v>-0.0015</v>
+        <v>-0.0016</v>
       </c>
       <c r="J614" t="n">
-        <v>-0.0345</v>
+        <v>-0.0368</v>
       </c>
     </row>
     <row r="615">
@@ -28789,10 +28789,10 @@
         <v>0.87</v>
       </c>
       <c r="I615" t="n">
-        <v>-0.1827</v>
+        <v>-0.1828</v>
       </c>
       <c r="J615" t="n">
-        <v>-4.2021</v>
+        <v>-4.2044</v>
       </c>
     </row>
     <row r="616">
@@ -28829,10 +28829,10 @@
         <v>0.64</v>
       </c>
       <c r="I616" t="n">
-        <v>-0.4043</v>
+        <v>-0.4044</v>
       </c>
       <c r="J616" t="n">
-        <v>-9.2989</v>
+        <v>-9.3012</v>
       </c>
     </row>
     <row r="617">
@@ -28869,10 +28869,10 @@
         <v>1.6</v>
       </c>
       <c r="I617" t="n">
-        <v>1.2468</v>
+        <v>1.2462</v>
       </c>
       <c r="J617" t="n">
-        <v>28.6764</v>
+        <v>28.6626</v>
       </c>
     </row>
     <row r="618">
@@ -28906,13 +28906,13 @@
         <v>23</v>
       </c>
       <c r="H618" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I618" t="n">
-        <v>0.9735</v>
+        <v>0.9903</v>
       </c>
       <c r="J618" t="n">
-        <v>22.3905</v>
+        <v>22.7769</v>
       </c>
     </row>
     <row r="619">
@@ -28949,10 +28949,10 @@
         <v>1.08</v>
       </c>
       <c r="I619" t="n">
-        <v>0.2613</v>
+        <v>0.261</v>
       </c>
       <c r="J619" t="n">
-        <v>6.0099</v>
+        <v>6.003</v>
       </c>
     </row>
     <row r="620">
@@ -28989,10 +28989,10 @@
         <v>0.99</v>
       </c>
       <c r="I620" t="n">
-        <v>-0.08840000000000001</v>
+        <v>-0.0888</v>
       </c>
       <c r="J620" t="n">
-        <v>-2.0332</v>
+        <v>-2.0424</v>
       </c>
     </row>
     <row r="621">
@@ -29029,10 +29029,10 @@
         <v>0.78</v>
       </c>
       <c r="I621" t="n">
-        <v>-0.6661</v>
+        <v>-0.6664</v>
       </c>
       <c r="J621" t="n">
-        <v>-15.3203</v>
+        <v>-15.3272</v>
       </c>
     </row>
     <row r="622">
@@ -29069,10 +29069,10 @@
         <v>0.89</v>
       </c>
       <c r="I622" t="n">
-        <v>-0.0912</v>
+        <v>-0.0919</v>
       </c>
       <c r="J622" t="n">
-        <v>-1.2768</v>
+        <v>-1.2866</v>
       </c>
     </row>
     <row r="623">
@@ -29109,10 +29109,10 @@
         <v>0.63</v>
       </c>
       <c r="I623" t="n">
-        <v>-0.3669</v>
+        <v>-0.3672</v>
       </c>
       <c r="J623" t="n">
-        <v>-5.1366</v>
+        <v>-5.1408</v>
       </c>
     </row>
     <row r="624">
@@ -29146,13 +29146,13 @@
         <v>14</v>
       </c>
       <c r="H624" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="I624" t="n">
-        <v>-0.4013</v>
+        <v>-0.3933</v>
       </c>
       <c r="J624" t="n">
-        <v>-5.6182</v>
+        <v>-5.5062</v>
       </c>
     </row>
     <row r="625">
@@ -29189,10 +29189,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I625" t="n">
-        <v>-0.4263</v>
+        <v>-0.4266</v>
       </c>
       <c r="J625" t="n">
-        <v>-5.9682</v>
+        <v>-5.9724</v>
       </c>
     </row>
     <row r="626">
@@ -29229,10 +29229,10 @@
         <v>0.28</v>
       </c>
       <c r="I626" t="n">
-        <v>-0.673</v>
+        <v>-0.6732</v>
       </c>
       <c r="J626" t="n">
-        <v>-9.422000000000001</v>
+        <v>-9.424799999999999</v>
       </c>
     </row>
     <row r="627">
@@ -29269,10 +29269,10 @@
         <v>2.1</v>
       </c>
       <c r="I627" t="n">
-        <v>1.7453</v>
+        <v>1.7456</v>
       </c>
       <c r="J627" t="n">
-        <v>24.4342</v>
+        <v>24.4384</v>
       </c>
     </row>
     <row r="628">
@@ -29306,13 +29306,13 @@
         <v>14</v>
       </c>
       <c r="H628" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="I628" t="n">
-        <v>1.7343</v>
+        <v>1.7235</v>
       </c>
       <c r="J628" t="n">
-        <v>24.2802</v>
+        <v>24.129</v>
       </c>
     </row>
     <row r="629">
@@ -29349,10 +29349,10 @@
         <v>1.95</v>
       </c>
       <c r="I629" t="n">
-        <v>1.5779</v>
+        <v>1.5782</v>
       </c>
       <c r="J629" t="n">
-        <v>22.0906</v>
+        <v>22.0948</v>
       </c>
     </row>
     <row r="630">
@@ -29389,10 +29389,10 @@
         <v>1.67</v>
       </c>
       <c r="I630" t="n">
-        <v>1.2573</v>
+        <v>1.2574</v>
       </c>
       <c r="J630" t="n">
-        <v>17.6022</v>
+        <v>17.6036</v>
       </c>
     </row>
     <row r="631">
@@ -29429,10 +29429,10 @@
         <v>0.75</v>
       </c>
       <c r="I631" t="n">
-        <v>-0.7989000000000001</v>
+        <v>-0.7987</v>
       </c>
       <c r="J631" t="n">
-        <v>-11.1846</v>
+        <v>-11.1818</v>
       </c>
     </row>
     <row r="632">
@@ -29869,10 +29869,10 @@
         <v>1.33</v>
       </c>
       <c r="I642" t="n">
-        <v>0.8282</v>
+        <v>0.8288</v>
       </c>
       <c r="J642" t="n">
-        <v>19.8768</v>
+        <v>19.8912</v>
       </c>
     </row>
     <row r="643">
@@ -29909,10 +29909,10 @@
         <v>1.17</v>
       </c>
       <c r="I643" t="n">
-        <v>0.4866</v>
+        <v>0.4869</v>
       </c>
       <c r="J643" t="n">
-        <v>11.6784</v>
+        <v>11.6856</v>
       </c>
     </row>
     <row r="644">
@@ -29949,10 +29949,10 @@
         <v>1.15</v>
       </c>
       <c r="I644" t="n">
-        <v>0.4407</v>
+        <v>0.441</v>
       </c>
       <c r="J644" t="n">
-        <v>10.5768</v>
+        <v>10.584</v>
       </c>
     </row>
     <row r="645">
@@ -29989,10 +29989,10 @@
         <v>1.12</v>
       </c>
       <c r="I645" t="n">
-        <v>0.3703</v>
+        <v>0.3705</v>
       </c>
       <c r="J645" t="n">
-        <v>8.8872</v>
+        <v>8.891999999999999</v>
       </c>
     </row>
     <row r="646">
@@ -30026,13 +30026,13 @@
         <v>24</v>
       </c>
       <c r="H646" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="I646" t="n">
-        <v>-0.3416</v>
+        <v>-0.3682</v>
       </c>
       <c r="J646" t="n">
-        <v>-8.198399999999999</v>
+        <v>-8.8368</v>
       </c>
     </row>
     <row r="647">
@@ -30066,13 +30066,13 @@
         <v>24</v>
       </c>
       <c r="H647" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="I647" t="n">
-        <v>0.3055</v>
+        <v>0.3241</v>
       </c>
       <c r="J647" t="n">
-        <v>7.332</v>
+        <v>7.7784</v>
       </c>
     </row>
     <row r="648">
@@ -30109,10 +30109,10 @@
         <v>1.04</v>
       </c>
       <c r="I648" t="n">
-        <v>0.1358</v>
+        <v>0.1354</v>
       </c>
       <c r="J648" t="n">
-        <v>3.2592</v>
+        <v>3.2496</v>
       </c>
     </row>
     <row r="649">
@@ -30149,10 +30149,10 @@
         <v>1</v>
       </c>
       <c r="I649" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0081</v>
       </c>
       <c r="J649" t="n">
-        <v>0.2016</v>
+        <v>0.1944</v>
       </c>
     </row>
     <row r="650">
@@ -30189,10 +30189,10 @@
         <v>0.83</v>
       </c>
       <c r="I650" t="n">
-        <v>-0.2161</v>
+        <v>-0.2163</v>
       </c>
       <c r="J650" t="n">
-        <v>-5.1864</v>
+        <v>-5.1912</v>
       </c>
     </row>
     <row r="651">
@@ -30229,10 +30229,10 @@
         <v>0.68</v>
       </c>
       <c r="I651" t="n">
-        <v>-0.3599</v>
+        <v>-0.3601</v>
       </c>
       <c r="J651" t="n">
-        <v>-8.637600000000001</v>
+        <v>-8.6424</v>
       </c>
     </row>
     <row r="652">
@@ -30669,10 +30669,10 @@
         <v>1.7</v>
       </c>
       <c r="I662" t="n">
-        <v>1.1711</v>
+        <v>1.1703</v>
       </c>
       <c r="J662" t="n">
-        <v>24.5931</v>
+        <v>24.5763</v>
       </c>
     </row>
     <row r="663">
@@ -30709,10 +30709,10 @@
         <v>1.12</v>
       </c>
       <c r="I663" t="n">
-        <v>0.3134</v>
+        <v>0.3129</v>
       </c>
       <c r="J663" t="n">
-        <v>6.5814</v>
+        <v>6.5709</v>
       </c>
     </row>
     <row r="664">
@@ -30749,10 +30749,10 @@
         <v>0.7</v>
       </c>
       <c r="I664" t="n">
-        <v>-0.3386</v>
+        <v>-0.3388</v>
       </c>
       <c r="J664" t="n">
-        <v>-7.1106</v>
+        <v>-7.1148</v>
       </c>
     </row>
     <row r="665">
@@ -30786,13 +30786,13 @@
         <v>21</v>
       </c>
       <c r="H665" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="I665" t="n">
-        <v>-0.411</v>
+        <v>-0.4023</v>
       </c>
       <c r="J665" t="n">
-        <v>-8.631</v>
+        <v>-8.4483</v>
       </c>
     </row>
     <row r="666">
@@ -30829,10 +30829,10 @@
         <v>0.38</v>
       </c>
       <c r="I666" t="n">
-        <v>-0.6161</v>
+        <v>-0.6162</v>
       </c>
       <c r="J666" t="n">
-        <v>-12.9381</v>
+        <v>-12.9402</v>
       </c>
     </row>
     <row r="667">
@@ -31869,10 +31869,10 @@
         <v>1.86</v>
       </c>
       <c r="I692" t="n">
-        <v>1.5223</v>
+        <v>1.5227</v>
       </c>
       <c r="J692" t="n">
-        <v>28.9237</v>
+        <v>28.9313</v>
       </c>
     </row>
     <row r="693">
@@ -31909,10 +31909,10 @@
         <v>1.59</v>
       </c>
       <c r="I693" t="n">
-        <v>1.1874</v>
+        <v>1.1877</v>
       </c>
       <c r="J693" t="n">
-        <v>22.5606</v>
+        <v>22.5663</v>
       </c>
     </row>
     <row r="694">
@@ -31946,13 +31946,13 @@
         <v>19</v>
       </c>
       <c r="H694" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="I694" t="n">
-        <v>1.1874</v>
+        <v>1.1749</v>
       </c>
       <c r="J694" t="n">
-        <v>22.5606</v>
+        <v>22.3231</v>
       </c>
     </row>
     <row r="695">
@@ -31989,10 +31989,10 @@
         <v>1.02</v>
       </c>
       <c r="I695" t="n">
-        <v>0.0345</v>
+        <v>0.0348</v>
       </c>
       <c r="J695" t="n">
-        <v>0.6555</v>
+        <v>0.6612</v>
       </c>
     </row>
     <row r="696">
@@ -32029,10 +32029,10 @@
         <v>0.96</v>
       </c>
       <c r="I696" t="n">
-        <v>-0.2382</v>
+        <v>-0.2379</v>
       </c>
       <c r="J696" t="n">
-        <v>-4.5258</v>
+        <v>-4.5201</v>
       </c>
     </row>
     <row r="697">
